--- a/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
+++ b/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
@@ -314,37 +314,7 @@
       <strike val="0"/>
       <u val="none"/>
       <sz val="12"/>
-      <color theme="2"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="12"/>
-      <color theme="2"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FF262626"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -368,6 +338,36 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="12"/>
+      <color theme="2"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF262626"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="12"/>
+      <color theme="2"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -375,6 +375,18 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4FF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -390,7 +402,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFD6DCE4"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -400,61 +412,12 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6DCE4"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF4FF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -474,45 +437,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thick">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thick">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color rgb="FFFFFFFF"/>
       </left>
       <right/>
-      <top style="thick">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FFFFFFFF"/>
-      </right>
       <top style="thick">
         <color rgb="FFFFFFFF"/>
       </top>
@@ -533,7 +461,88 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFFFF"/>
+      </left>
       <right style="thick">
         <color rgb="FFFFFFFF"/>
       </right>
@@ -554,193 +563,217 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="5" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="5" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="4" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="4" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="4" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="5" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="5" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="5" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="4" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="4" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="14" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="164" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="165" fillId="7" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="165" fillId="7" borderId="4" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="true">
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+      <protection locked="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1128,986 +1161,986 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customHeight="1" ht="28">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12" customHeight="1" ht="70">
-      <c r="A2" s="11"/>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="11"/>
+      <c r="A2" s="16"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="11"/>
-      <c r="B3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="11"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="11"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="11"/>
+      <c r="A4" s="16"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" customHeight="1" ht="34">
-      <c r="A5" s="11"/>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="11"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" customHeight="1" ht="23">
-      <c r="A6" s="11"/>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="11"/>
-    </row>
-    <row r="7" spans="1:12" customHeight="1" ht="6" s="3" customFormat="1">
-      <c r="A7" s="11"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="11"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" customHeight="1" ht="6" s="1" customFormat="1">
+      <c r="A7" s="16"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" customHeight="1" ht="23">
-      <c r="A8" s="11"/>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="5" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="5" t="s">
+      <c r="G8" s="5"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="51"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="11"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" customHeight="1" ht="23">
-      <c r="A9" s="11"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="11"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" customHeight="1" ht="23">
-      <c r="A10" s="11"/>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="11"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" customHeight="1" ht="5">
-      <c r="A11" s="11"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="11"/>
+      <c r="A11" s="16"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" customHeight="1" ht="23">
-      <c r="A12" s="11"/>
-      <c r="B12" s="10" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="11"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" customHeight="1" ht="23">
-      <c r="A13" s="11"/>
-      <c r="B13" s="18" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="11"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" customHeight="1" ht="23">
-      <c r="A14" s="11"/>
-      <c r="B14" s="18" t="s">
+      <c r="A14" s="16"/>
+      <c r="B14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="11"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" customHeight="1" ht="23">
-      <c r="A15" s="11"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="11"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" customHeight="1" ht="23">
-      <c r="A16" s="11"/>
-      <c r="B16" s="4" t="s">
+      <c r="A16" s="16"/>
+      <c r="B16" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="11"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" customHeight="1" ht="5">
-      <c r="A17" s="11"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="11"/>
+      <c r="A17" s="16"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="21"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" customHeight="1" ht="23">
-      <c r="A18" s="11"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="11"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" customHeight="1" ht="23">
-      <c r="A19" s="11"/>
-      <c r="B19" s="19" t="s">
+      <c r="A19" s="16"/>
+      <c r="B19" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="20"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="23" t="s">
+      <c r="C19" s="29"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="11"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" customHeight="1" ht="23">
-      <c r="A20" s="11"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="11"/>
+      <c r="A20" s="16"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" customHeight="1" ht="23">
-      <c r="A21" s="11"/>
-      <c r="B21" s="2" t="s">
+      <c r="A21" s="16"/>
+      <c r="B21" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="11"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" customHeight="1" ht="5">
-      <c r="A22" s="11"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="11"/>
+      <c r="A22" s="16"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" customHeight="1" ht="23">
-      <c r="A23" s="11"/>
+      <c r="A23" s="16"/>
       <c r="B23" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="26" t="s">
+      <c r="C23" s="29"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="27"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="11"/>
+      <c r="H23" s="47"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" customHeight="1" ht="23">
-      <c r="A24" s="11"/>
-      <c r="B24" s="19" t="s">
+      <c r="A24" s="16"/>
+      <c r="B24" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="21"/>
-      <c r="G24" s="26" t="s">
+      <c r="C24" s="29"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="27"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="11"/>
+      <c r="H24" s="47"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" customHeight="1" ht="23">
-      <c r="A25" s="11"/>
-      <c r="B25" s="19" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="28" t="s">
+      <c r="C25" s="29"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="29"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="11"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" customHeight="1" ht="23">
-      <c r="A26" s="11"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="11"/>
+      <c r="A26" s="16"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" customHeight="1" ht="23">
-      <c r="A27" s="11"/>
-      <c r="B27" s="2" t="s">
+      <c r="A27" s="16"/>
+      <c r="B27" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="11"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" customHeight="1" ht="5">
-      <c r="A28" s="11"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="11"/>
+      <c r="A28" s="16"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" customHeight="1" ht="23">
-      <c r="A29" s="11"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="33"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="11"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="47"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" customHeight="1" ht="23">
-      <c r="A30" s="11"/>
-      <c r="B30" s="19" t="s">
+      <c r="A30" s="16"/>
+      <c r="B30" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="26" t="s">
+      <c r="C30" s="29"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="H30" s="27"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="11"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" customHeight="1" ht="23">
-      <c r="A31" s="11"/>
-      <c r="B31" s="19" t="s">
+      <c r="A31" s="16"/>
+      <c r="B31" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="20"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="28" t="s">
+      <c r="C31" s="29"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="29"/>
-      <c r="I31" s="53"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="11"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" customHeight="1" ht="23">
-      <c r="A32" s="11"/>
-      <c r="B32" s="19" t="s">
+      <c r="A32" s="16"/>
+      <c r="B32" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="11"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" customHeight="1" ht="23">
-      <c r="A33" s="11"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="11"/>
+      <c r="A33" s="16"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+      <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" customHeight="1" ht="23">
-      <c r="A34" s="11"/>
-      <c r="B34" s="2" t="s">
+      <c r="A34" s="16"/>
+      <c r="B34" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="11"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" customHeight="1" ht="5">
-      <c r="A35" s="11"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="11"/>
+      <c r="A35" s="16"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="21"/>
+      <c r="L35" s="2"/>
     </row>
     <row r="36" spans="1:12" customHeight="1" ht="23">
-      <c r="A36" s="11"/>
-      <c r="B36" s="10" t="s">
+      <c r="A36" s="16"/>
+      <c r="B36" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="45"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="17"/>
-      <c r="L36" s="11"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="53"/>
+      <c r="L36" s="2"/>
     </row>
     <row r="37" spans="1:12" customHeight="1" ht="23">
-      <c r="A37" s="11"/>
-      <c r="B37" s="18" t="s">
+      <c r="A37" s="16"/>
+      <c r="B37" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="45"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="11"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="23"/>
+      <c r="L37" s="2"/>
     </row>
     <row r="38" spans="1:12" customHeight="1" ht="23">
-      <c r="A38" s="11"/>
-      <c r="B38" s="18" t="s">
+      <c r="A38" s="16"/>
+      <c r="B38" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="45"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="11"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="23"/>
+      <c r="L38" s="2"/>
     </row>
     <row r="39" spans="1:12" customHeight="1" ht="23">
-      <c r="A39" s="11"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
-      <c r="L39" s="11"/>
+      <c r="A39" s="16"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+      <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12" customHeight="1" ht="23">
-      <c r="A40" s="11"/>
-      <c r="B40" s="2" t="s">
+      <c r="A40" s="16"/>
+      <c r="B40" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="11"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" customHeight="1" ht="5">
-      <c r="A41" s="11"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="6"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="11"/>
+      <c r="A41" s="16"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
+      <c r="L41" s="2"/>
     </row>
     <row r="42" spans="1:12" customHeight="1" ht="23">
-      <c r="A42" s="11"/>
-      <c r="B42" s="10" t="s">
+      <c r="A42" s="16"/>
+      <c r="B42" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="45"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="17"/>
-      <c r="L42" s="11"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="53"/>
+      <c r="L42" s="2"/>
     </row>
     <row r="43" spans="1:12" customHeight="1" ht="23">
-      <c r="A43" s="11"/>
-      <c r="B43" s="18" t="s">
+      <c r="A43" s="16"/>
+      <c r="B43" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="45"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="11"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="2"/>
     </row>
     <row r="44" spans="1:12" customHeight="1" ht="23">
-      <c r="A44" s="11"/>
-      <c r="B44" s="18" t="s">
+      <c r="A44" s="16"/>
+      <c r="B44" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="45"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="11"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="23"/>
+      <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12" customHeight="1" ht="23">
-      <c r="A45" s="11"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="11"/>
+      <c r="A45" s="16"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="23"/>
+      <c r="K45" s="23"/>
+      <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12" customHeight="1" ht="23">
-      <c r="A46" s="11"/>
-      <c r="B46" s="2" t="s">
+      <c r="A46" s="16"/>
+      <c r="B46" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="11"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12" customHeight="1" ht="5">
-      <c r="A47" s="11"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="11"/>
+      <c r="A47" s="16"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" customHeight="1" ht="23">
-      <c r="A48" s="11"/>
-      <c r="B48" s="10" t="s">
+      <c r="A48" s="16"/>
+      <c r="B48" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="22" t="s">
+      <c r="C48" s="8"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="F48" s="46"/>
-      <c r="G48" s="46"/>
-      <c r="H48" s="22" t="s">
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="I48" s="47"/>
-      <c r="J48" s="55"/>
-      <c r="K48" s="54"/>
-      <c r="L48" s="11"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="52"/>
+      <c r="K48" s="34"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" customHeight="1" ht="23">
-      <c r="A49" s="11"/>
-      <c r="B49" s="35" t="s">
+      <c r="A49" s="16"/>
+      <c r="B49" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C49" s="49"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="22" t="s">
+      <c r="C49" s="11"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="F49" s="46"/>
-      <c r="G49" s="46"/>
-      <c r="H49" s="22" t="s">
+      <c r="F49" s="8"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="I49" s="47"/>
-      <c r="J49" s="55"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="11"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="52"/>
+      <c r="K49" s="34"/>
+      <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" customHeight="1" ht="23">
-      <c r="A50" s="11"/>
-      <c r="B50" s="35" t="s">
+      <c r="A50" s="16"/>
+      <c r="B50" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="49"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="22" t="s">
+      <c r="C50" s="11"/>
+      <c r="D50" s="34"/>
+      <c r="E50" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="F50" s="46"/>
-      <c r="G50" s="46"/>
-      <c r="H50" s="22" t="s">
+      <c r="F50" s="8"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="I50" s="47"/>
-      <c r="J50" s="55"/>
-      <c r="K50" s="54"/>
-      <c r="L50" s="11"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="52"/>
+      <c r="K50" s="34"/>
+      <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" customHeight="1" ht="23">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
+      <c r="A51" s="16"/>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
+      <c r="G51" s="16"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" customHeight="1" ht="23">
-      <c r="A52" s="11"/>
-      <c r="B52" s="2" t="s">
+      <c r="A52" s="16"/>
+      <c r="B52" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-      <c r="L52" s="11"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" customHeight="1" ht="5">
-      <c r="A53" s="11"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="11"/>
+      <c r="A53" s="16"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="21"/>
+      <c r="G53" s="21"/>
+      <c r="H53" s="21"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" customHeight="1" ht="23">
-      <c r="A54" s="11"/>
+      <c r="A54" s="16"/>
       <c r="B54" s="24"/>
-      <c r="C54" s="20"/>
-      <c r="D54" s="50"/>
-      <c r="E54" s="36" t="s">
+      <c r="C54" s="29"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="37"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="37"/>
-      <c r="I54" s="37"/>
-      <c r="J54" s="37"/>
-      <c r="K54" s="38"/>
-      <c r="L54" s="11"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
+      <c r="I54" s="44"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="54"/>
+      <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-      <c r="H55" s="11"/>
-      <c r="I55" s="11"/>
-      <c r="J55" s="11"/>
-      <c r="K55" s="11"/>
-      <c r="L55" s="11"/>
+      <c r="A55" s="16"/>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="11"/>
-      <c r="B56" s="39" t="s">
+      <c r="A56" s="16"/>
+      <c r="B56" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="40"/>
-      <c r="D56" s="40"/>
-      <c r="E56" s="40"/>
-      <c r="F56" s="40"/>
-      <c r="G56" s="40"/>
-      <c r="H56" s="40"/>
-      <c r="I56" s="40"/>
-      <c r="J56" s="40"/>
-      <c r="K56" s="40"/>
-      <c r="L56" s="11"/>
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+      <c r="F56" s="28"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28"/>
+      <c r="I56" s="28"/>
+      <c r="J56" s="28"/>
+      <c r="K56" s="28"/>
+      <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="11"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="40"/>
-      <c r="I57" s="40"/>
-      <c r="J57" s="40"/>
-      <c r="K57" s="40"/>
-      <c r="L57" s="11"/>
+      <c r="A57" s="16"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="28"/>
+      <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="11"/>
-      <c r="B58" s="40"/>
-      <c r="C58" s="40"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="40"/>
-      <c r="F58" s="40"/>
-      <c r="G58" s="40"/>
-      <c r="H58" s="40"/>
-      <c r="I58" s="40"/>
-      <c r="J58" s="40"/>
-      <c r="K58" s="40"/>
-      <c r="L58" s="11"/>
+      <c r="A58" s="16"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="11"/>
-      <c r="B59" s="40"/>
-      <c r="C59" s="40"/>
-      <c r="D59" s="40"/>
-      <c r="E59" s="40"/>
-      <c r="F59" s="40"/>
-      <c r="G59" s="40"/>
-      <c r="H59" s="40"/>
-      <c r="I59" s="40"/>
-      <c r="J59" s="40"/>
-      <c r="K59" s="40"/>
-      <c r="L59" s="11"/>
+      <c r="A59" s="16"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="28"/>
+      <c r="F59" s="28"/>
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="11"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="40"/>
-      <c r="F60" s="40"/>
-      <c r="G60" s="40"/>
-      <c r="H60" s="40"/>
-      <c r="I60" s="40"/>
-      <c r="J60" s="40"/>
-      <c r="K60" s="40"/>
-      <c r="L60" s="11"/>
+      <c r="A60" s="16"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="28"/>
+      <c r="H60" s="28"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="28"/>
+      <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
-      <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
-      <c r="I61" s="11"/>
-      <c r="J61" s="11"/>
-      <c r="K61" s="11"/>
-      <c r="L61" s="11"/>
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
-      <c r="G62" s="11"/>
-      <c r="H62" s="11"/>
-      <c r="I62" s="11"/>
-      <c r="J62" s="11"/>
-      <c r="K62" s="11"/>
-      <c r="L62" s="11"/>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
-      <c r="G63" s="11"/>
-      <c r="H63" s="11"/>
-      <c r="I63" s="11"/>
-      <c r="J63" s="11"/>
-      <c r="K63" s="11"/>
-      <c r="L63" s="11"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection password="9328" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteColumns="0" deleteRows="0" sort="1"/>
+  <sheetProtection password="9328" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteColumns="0" deleteRows="0" sort="0" selectLockedCells="0" selectUnlockedCells="1"/>
   <mergeCells>
     <mergeCell ref="B56:K60"/>
     <mergeCell ref="B52:K52"/>
@@ -2230,119 +2263,119 @@
   <dimension ref="A1:AL2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:38" s="41" customFormat="1">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:38" s="3" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I1" s="41" t="s">
+      <c r="I1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J1" s="41" t="s">
+      <c r="J1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="L1" s="41" t="s">
+      <c r="L1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M1" s="41" t="s">
+      <c r="M1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="N1" s="41" t="s">
+      <c r="N1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="O1" s="41" t="s">
+      <c r="O1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="P1" s="41" t="s">
+      <c r="P1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="Q1" s="41" t="s">
+      <c r="Q1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="R1" s="41" t="s">
+      <c r="R1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="S1" s="41" t="s">
+      <c r="S1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="T1" s="41" t="s">
+      <c r="T1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="U1" s="41" t="s">
+      <c r="U1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="V1" s="41" t="s">
+      <c r="V1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="W1" s="41" t="s">
+      <c r="W1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="X1" s="41" t="s">
+      <c r="X1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="Y1" s="41" t="s">
+      <c r="Y1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="Z1" s="41" t="s">
+      <c r="Z1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="AA1" s="41" t="s">
+      <c r="AA1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="AB1" s="41" t="s">
+      <c r="AB1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="AC1" s="41" t="s">
+      <c r="AC1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AD1" s="41" t="s">
+      <c r="AD1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="AE1" s="41" t="s">
+      <c r="AE1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="AF1" s="41" t="s">
+      <c r="AF1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="AG1" s="41" t="s">
+      <c r="AG1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="AH1" s="41" t="s">
+      <c r="AH1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="AI1" s="41" t="s">
+      <c r="AI1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="AJ1" s="41" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AK1" s="41" t="s">
+      <c r="AK1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AL1" s="41" t="s">
+      <c r="AL1" s="3" t="s">
         <v>80</v>
       </c>
     </row>

--- a/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
+++ b/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
@@ -567,7 +567,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
@@ -600,179 +600,183 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="true">
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="true">
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
       <protection locked="true"/>
     </xf>
   </cellXfs>
@@ -1161,941 +1165,941 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customHeight="1" ht="28">
-      <c r="A1" s="16"/>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
       <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12" customHeight="1" ht="70">
-      <c r="A2" s="16"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="16"/>
-      <c r="B3" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="16"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" customHeight="1" ht="34">
-      <c r="A5" s="16"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
       <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" customHeight="1" ht="23">
-      <c r="A6" s="16"/>
-      <c r="B6" s="20" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
       <c r="L6" s="2"/>
     </row>
     <row r="7" spans="1:12" customHeight="1" ht="6" s="1" customFormat="1">
-      <c r="A7" s="16"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
+      <c r="A7" s="15"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
       <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" customHeight="1" ht="23">
-      <c r="A8" s="16"/>
-      <c r="B8" s="22" t="s">
+      <c r="A8" s="15"/>
+      <c r="B8" s="21" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="22" t="s">
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="21" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="22" t="s">
+      <c r="H8" s="35"/>
+      <c r="I8" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="36"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="35"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" customHeight="1" ht="23">
-      <c r="A9" s="16"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="23"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" spans="1:12" customHeight="1" ht="23">
-      <c r="A10" s="16"/>
-      <c r="B10" s="20" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="19"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" customHeight="1" ht="5">
-      <c r="A11" s="16"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="21"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" customHeight="1" ht="23">
-      <c r="A12" s="16"/>
-      <c r="B12" s="24" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="23" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="7"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="53"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="52"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" customHeight="1" ht="23">
-      <c r="A13" s="16"/>
-      <c r="B13" s="24" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="7"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="23"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="22"/>
       <c r="L13" s="2"/>
     </row>
     <row r="14" spans="1:12" customHeight="1" ht="23">
-      <c r="A14" s="16"/>
-      <c r="B14" s="24" t="s">
+      <c r="A14" s="15"/>
+      <c r="B14" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="23"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="22"/>
       <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:12" customHeight="1" ht="23">
-      <c r="A15" s="16"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
       <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:12" customHeight="1" ht="23">
-      <c r="A16" s="16"/>
-      <c r="B16" s="25" t="s">
+      <c r="A16" s="15"/>
+      <c r="B16" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
       <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" customHeight="1" ht="5">
-      <c r="A17" s="16"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="21"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
       <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" customHeight="1" ht="23">
-      <c r="A18" s="16"/>
-      <c r="B18" s="24" t="s">
+      <c r="A18" s="15"/>
+      <c r="B18" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="24"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="4"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
       <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" customHeight="1" ht="23">
-      <c r="A19" s="16"/>
-      <c r="B19" s="24" t="s">
+      <c r="A19" s="15"/>
+      <c r="B19" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="29"/>
+      <c r="C19" s="28"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="34" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="7"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" customHeight="1" ht="23">
-      <c r="A20" s="16"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" customHeight="1" ht="23">
-      <c r="A21" s="16"/>
-      <c r="B21" s="20" t="s">
+      <c r="A21" s="15"/>
+      <c r="B21" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" customHeight="1" ht="5">
-      <c r="A22" s="16"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-      <c r="K22" s="21"/>
+      <c r="A22" s="15"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" customHeight="1" ht="23">
-      <c r="A23" s="16"/>
-      <c r="B23" s="24" t="s">
+      <c r="A23" s="15"/>
+      <c r="B23" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="45" t="s">
+      <c r="C23" s="28"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="47"/>
+      <c r="H23" s="46"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" customHeight="1" ht="23">
-      <c r="A24" s="16"/>
-      <c r="B24" s="24" t="s">
+      <c r="A24" s="15"/>
+      <c r="B24" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="29"/>
+      <c r="C24" s="28"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="45" t="s">
+      <c r="E24" s="36"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="47"/>
+      <c r="H24" s="46"/>
       <c r="I24" s="9"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="37"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="36"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" customHeight="1" ht="23">
-      <c r="A25" s="16"/>
-      <c r="B25" s="24" t="s">
+      <c r="A25" s="15"/>
+      <c r="B25" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C25" s="29"/>
+      <c r="C25" s="28"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="46" t="s">
+      <c r="E25" s="37"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="48"/>
+      <c r="H25" s="47"/>
       <c r="I25" s="8"/>
-      <c r="J25" s="50"/>
-      <c r="K25" s="50"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="49"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" customHeight="1" ht="23">
-      <c r="A26" s="16"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
       <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" customHeight="1" ht="23">
-      <c r="A27" s="16"/>
-      <c r="B27" s="20" t="s">
+      <c r="A27" s="15"/>
+      <c r="B27" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
       <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" customHeight="1" ht="5">
-      <c r="A28" s="16"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="21"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
       <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" customHeight="1" ht="23">
-      <c r="A29" s="16"/>
-      <c r="B29" s="24" t="s">
+      <c r="A29" s="15"/>
+      <c r="B29" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="29"/>
+      <c r="C29" s="28"/>
       <c r="D29" s="6"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" customHeight="1" ht="23">
-      <c r="A30" s="16"/>
-      <c r="B30" s="24" t="s">
+      <c r="A30" s="15"/>
+      <c r="B30" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="45" t="s">
+      <c r="C30" s="28"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="H30" s="47"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="37"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="36"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" customHeight="1" ht="23">
-      <c r="A31" s="16"/>
-      <c r="B31" s="24" t="s">
+      <c r="A31" s="15"/>
+      <c r="B31" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="46" t="s">
+      <c r="C31" s="28"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="48"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="50"/>
-      <c r="K31" s="50"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="49"/>
+      <c r="K31" s="49"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" customHeight="1" ht="23">
-      <c r="A32" s="16"/>
-      <c r="B32" s="24" t="s">
+      <c r="A32" s="15"/>
+      <c r="B32" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="47"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" customHeight="1" ht="23">
-      <c r="A33" s="16"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23"/>
-      <c r="K33" s="23"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" customHeight="1" ht="23">
-      <c r="A34" s="16"/>
-      <c r="B34" s="20" t="s">
+      <c r="A34" s="15"/>
+      <c r="B34" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" customHeight="1" ht="5">
-      <c r="A35" s="16"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-      <c r="K35" s="21"/>
+      <c r="A35" s="15"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
       <c r="L35" s="2"/>
     </row>
     <row r="36" spans="1:12" customHeight="1" ht="23">
-      <c r="A36" s="16"/>
-      <c r="B36" s="24" t="s">
+      <c r="A36" s="15"/>
+      <c r="B36" s="23" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="7"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="53"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="52"/>
       <c r="L36" s="2"/>
     </row>
     <row r="37" spans="1:12" customHeight="1" ht="23">
-      <c r="A37" s="16"/>
-      <c r="B37" s="24" t="s">
+      <c r="A37" s="15"/>
+      <c r="B37" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="7"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="23"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="22"/>
       <c r="L37" s="2"/>
     </row>
     <row r="38" spans="1:12" customHeight="1" ht="23">
-      <c r="A38" s="16"/>
-      <c r="B38" s="24" t="s">
+      <c r="A38" s="15"/>
+      <c r="B38" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="7"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="23"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="22"/>
       <c r="L38" s="2"/>
     </row>
     <row r="39" spans="1:12" customHeight="1" ht="23">
-      <c r="A39" s="16"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="23"/>
-      <c r="I39" s="23"/>
-      <c r="J39" s="23"/>
-      <c r="K39" s="23"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12" customHeight="1" ht="23">
-      <c r="A40" s="16"/>
-      <c r="B40" s="20" t="s">
+      <c r="A40" s="15"/>
+      <c r="B40" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
       <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" customHeight="1" ht="5">
-      <c r="A41" s="16"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="21"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21"/>
-      <c r="K41" s="21"/>
+      <c r="A41" s="15"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
       <c r="L41" s="2"/>
     </row>
     <row r="42" spans="1:12" customHeight="1" ht="23">
-      <c r="A42" s="16"/>
-      <c r="B42" s="24" t="s">
+      <c r="A42" s="15"/>
+      <c r="B42" s="23" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="7"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="53"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="52"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="1:12" customHeight="1" ht="23">
-      <c r="A43" s="16"/>
-      <c r="B43" s="24" t="s">
+      <c r="A43" s="15"/>
+      <c r="B43" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="7"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="23"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="22"/>
       <c r="L43" s="2"/>
     </row>
     <row r="44" spans="1:12" customHeight="1" ht="23">
-      <c r="A44" s="16"/>
-      <c r="B44" s="24" t="s">
+      <c r="A44" s="15"/>
+      <c r="B44" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="7"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="23"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="22"/>
       <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12" customHeight="1" ht="23">
-      <c r="A45" s="16"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="23"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="23"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
       <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12" customHeight="1" ht="23">
-      <c r="A46" s="16"/>
-      <c r="B46" s="20" t="s">
+      <c r="A46" s="15"/>
+      <c r="B46" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
       <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12" customHeight="1" ht="5">
-      <c r="A47" s="16"/>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="21"/>
+      <c r="A47" s="15"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" customHeight="1" ht="23">
-      <c r="A48" s="16"/>
-      <c r="B48" s="24" t="s">
+      <c r="A48" s="15"/>
+      <c r="B48" s="23" t="s">
         <v>31</v>
       </c>
       <c r="C48" s="8"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="40" t="s">
+      <c r="D48" s="29"/>
+      <c r="E48" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="40" t="s">
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="I48" s="33"/>
-      <c r="J48" s="52"/>
-      <c r="K48" s="34"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="51"/>
+      <c r="K48" s="33"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" customHeight="1" ht="23">
-      <c r="A49" s="16"/>
-      <c r="B49" s="26" t="s">
+      <c r="A49" s="15"/>
+      <c r="B49" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C49" s="11"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="40" t="s">
+      <c r="C49" s="55"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="39" t="s">
         <v>35</v>
       </c>
       <c r="F49" s="8"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="40" t="s">
+      <c r="G49" s="29"/>
+      <c r="H49" s="39" t="s">
         <v>36</v>
       </c>
       <c r="I49" s="9"/>
-      <c r="J49" s="52"/>
-      <c r="K49" s="34"/>
+      <c r="J49" s="51"/>
+      <c r="K49" s="33"/>
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" customHeight="1" ht="23">
-      <c r="A50" s="16"/>
-      <c r="B50" s="26" t="s">
+      <c r="A50" s="15"/>
+      <c r="B50" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="11"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="40" t="s">
+      <c r="C50" s="55"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="39" t="s">
         <v>38</v>
       </c>
       <c r="F50" s="8"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="40" t="s">
+      <c r="G50" s="29"/>
+      <c r="H50" s="39" t="s">
         <v>39</v>
       </c>
       <c r="I50" s="9"/>
-      <c r="J50" s="52"/>
-      <c r="K50" s="34"/>
+      <c r="J50" s="51"/>
+      <c r="K50" s="33"/>
       <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" customHeight="1" ht="23">
-      <c r="A51" s="16"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
-      <c r="H51" s="16"/>
-      <c r="I51" s="16"/>
-      <c r="J51" s="16"/>
-      <c r="K51" s="16"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
       <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" customHeight="1" ht="23">
-      <c r="A52" s="16"/>
-      <c r="B52" s="20" t="s">
+      <c r="A52" s="15"/>
+      <c r="B52" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
-      <c r="G52" s="20"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
       <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" customHeight="1" ht="5">
-      <c r="A53" s="16"/>
-      <c r="B53" s="21"/>
-      <c r="C53" s="21"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="21"/>
-      <c r="H53" s="21"/>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21"/>
-      <c r="K53" s="21"/>
+      <c r="A53" s="15"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
       <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" customHeight="1" ht="23">
-      <c r="A54" s="16"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="41" t="s">
+      <c r="A54" s="15"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="44"/>
-      <c r="G54" s="44"/>
-      <c r="H54" s="44"/>
-      <c r="I54" s="44"/>
-      <c r="J54" s="44"/>
-      <c r="K54" s="54"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="43"/>
+      <c r="H54" s="43"/>
+      <c r="I54" s="43"/>
+      <c r="J54" s="43"/>
+      <c r="K54" s="53"/>
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="16"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
-      <c r="H55" s="16"/>
-      <c r="I55" s="16"/>
-      <c r="J55" s="16"/>
-      <c r="K55" s="16"/>
+      <c r="A55" s="15"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
       <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="16"/>
-      <c r="B56" s="27" t="s">
+      <c r="A56" s="15"/>
+      <c r="B56" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
-      <c r="J56" s="28"/>
-      <c r="K56" s="28"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="27"/>
+      <c r="K56" s="27"/>
       <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="16"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="27"/>
+      <c r="J57" s="27"/>
+      <c r="K57" s="27"/>
       <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="16"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
+      <c r="A58" s="15"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="27"/>
+      <c r="K58" s="27"/>
       <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="16"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="28"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28"/>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
-      <c r="K59" s="28"/>
+      <c r="A59" s="15"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+      <c r="K59" s="27"/>
       <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="16"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28"/>
-      <c r="K60" s="28"/>
+      <c r="A60" s="15"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27"/>
+      <c r="I60" s="27"/>
+      <c r="J60" s="27"/>
+      <c r="K60" s="27"/>
       <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12">
@@ -2140,7 +2144,7 @@
       <c r="L63" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection password="9328" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteColumns="0" deleteRows="0" sort="0" selectLockedCells="0" selectUnlockedCells="1"/>
+  <sheetProtection password="9328" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" deleteColumns="1" deleteRows="1" sort="1" selectLockedCells="0" selectUnlockedCells="0"/>
   <mergeCells>
     <mergeCell ref="B56:K60"/>
     <mergeCell ref="B52:K52"/>
@@ -2505,11 +2509,11 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <f>Solicitud!C49</f>
+        <f>Solicitud!D49</f>
         <v>0</v>
       </c>
       <c r="AG2">
-        <f>Solicitud!C50</f>
+        <f>Solicitud!D50</f>
         <v>0</v>
       </c>
       <c r="AH2">

--- a/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
+++ b/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
@@ -11,14 +11,14 @@
     <sheet name="Datos" sheetId="2" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="DatosSolicitud">'Datos'!A1:AL2</definedName>
+    <definedName name="DatosSolicitud">'Datos'!$A$1:$AN$2</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
   <si>
     <t>SOLICITUD DE ASEGURAMIENTO DE MERCANCIA</t>
   </si>
@@ -287,6 +287,12 @@
   </si>
   <si>
     <t>acepta_informacion_veridica</t>
+  </si>
+  <si>
+    <t>ref_maritimo</t>
+  </si>
+  <si>
+    <t>ref_aereo</t>
   </si>
 </sst>
 </file>
@@ -567,7 +573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
@@ -683,10 +689,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
       <protection locked="true"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true"/>
@@ -783,7 +785,89 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
   <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
@@ -1280,12 +1364,12 @@
         <v>4</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="35"/>
+      <c r="H8" s="34"/>
       <c r="I8" s="21" t="s">
         <v>5</v>
       </c>
       <c r="J8" s="12"/>
-      <c r="K8" s="35"/>
+      <c r="K8" s="34"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" customHeight="1" ht="23">
@@ -1345,7 +1429,7 @@
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
-      <c r="K12" s="52"/>
+      <c r="K12" s="51"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" customHeight="1" ht="23">
@@ -1447,7 +1531,7 @@
       </c>
       <c r="C19" s="28"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="33" t="s">
         <v>13</v>
       </c>
       <c r="F19" s="7"/>
@@ -1509,15 +1593,15 @@
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="12"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="44" t="s">
+      <c r="E23" s="34"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="H23" s="46"/>
+      <c r="H23" s="45"/>
       <c r="I23" s="8"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" customHeight="1" ht="23">
@@ -1527,15 +1611,15 @@
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="41"/>
-      <c r="G24" s="44" t="s">
+      <c r="E24" s="35"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="H24" s="46"/>
+      <c r="H24" s="45"/>
       <c r="I24" s="9"/>
-      <c r="J24" s="50"/>
-      <c r="K24" s="36"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="35"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" customHeight="1" ht="23">
@@ -1545,15 +1629,15 @@
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="45" t="s">
+      <c r="E25" s="36"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="47"/>
+      <c r="H25" s="46"/>
       <c r="I25" s="8"/>
-      <c r="J25" s="49"/>
-      <c r="K25" s="49"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" customHeight="1" ht="23">
@@ -1607,13 +1691,13 @@
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="6"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="48"/>
-      <c r="K29" s="48"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
       <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" customHeight="1" ht="23">
@@ -1623,15 +1707,15 @@
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="13"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="44" t="s">
+      <c r="E30" s="35"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="H30" s="46"/>
+      <c r="H30" s="45"/>
       <c r="I30" s="13"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="36"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="35"/>
       <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" customHeight="1" ht="23">
@@ -1641,15 +1725,15 @@
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="13"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="45" t="s">
+      <c r="E31" s="35"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="H31" s="47"/>
+      <c r="H31" s="46"/>
       <c r="I31" s="14"/>
-      <c r="J31" s="49"/>
-      <c r="K31" s="49"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
       <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" customHeight="1" ht="23">
@@ -1659,13 +1743,13 @@
       </c>
       <c r="C32" s="28"/>
       <c r="D32" s="13"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="47"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" customHeight="1" ht="23">
@@ -1725,7 +1809,7 @@
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="J36" s="31"/>
-      <c r="K36" s="52"/>
+      <c r="K36" s="51"/>
       <c r="L36" s="2"/>
     </row>
     <row r="37" spans="1:12" customHeight="1" ht="23">
@@ -1817,7 +1901,7 @@
       <c r="H42" s="31"/>
       <c r="I42" s="31"/>
       <c r="J42" s="31"/>
-      <c r="K42" s="52"/>
+      <c r="K42" s="51"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="1:12" customHeight="1" ht="23">
@@ -1903,17 +1987,17 @@
       </c>
       <c r="C48" s="8"/>
       <c r="D48" s="29"/>
-      <c r="E48" s="39" t="s">
+      <c r="E48" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="F48" s="29"/>
+      <c r="F48" s="8"/>
       <c r="G48" s="29"/>
-      <c r="H48" s="39" t="s">
+      <c r="H48" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="I48" s="32"/>
-      <c r="J48" s="51"/>
-      <c r="K48" s="33"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="50"/>
+      <c r="K48" s="32"/>
       <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" customHeight="1" ht="23">
@@ -1921,19 +2005,19 @@
       <c r="B49" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C49" s="55"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="39" t="s">
+      <c r="C49" s="54"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="38" t="s">
         <v>35</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="29"/>
-      <c r="H49" s="39" t="s">
+      <c r="H49" s="38" t="s">
         <v>36</v>
       </c>
       <c r="I49" s="9"/>
-      <c r="J49" s="51"/>
-      <c r="K49" s="33"/>
+      <c r="J49" s="50"/>
+      <c r="K49" s="32"/>
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" customHeight="1" ht="23">
@@ -1941,19 +2025,19 @@
       <c r="B50" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="C50" s="55"/>
-      <c r="D50" s="54"/>
-      <c r="E50" s="39" t="s">
+      <c r="C50" s="54"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="38" t="s">
         <v>38</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="29"/>
-      <c r="H50" s="39" t="s">
+      <c r="H50" s="38" t="s">
         <v>39</v>
       </c>
       <c r="I50" s="9"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="33"/>
+      <c r="J50" s="50"/>
+      <c r="K50" s="32"/>
       <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" customHeight="1" ht="23">
@@ -2005,15 +2089,15 @@
       <c r="B54" s="23"/>
       <c r="C54" s="28"/>
       <c r="D54" s="11"/>
-      <c r="E54" s="40" t="s">
+      <c r="E54" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="43"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="43"/>
-      <c r="I54" s="43"/>
-      <c r="J54" s="43"/>
-      <c r="K54" s="53"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="52"/>
       <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
@@ -2223,6 +2307,51 @@
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="G8:H8"/>
   </mergeCells>
+  <conditionalFormatting sqref="C8:E8">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>LEN(TRIM($C$8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12:J12">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>LEN(TRIM($C$12))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:K18">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>LEN(TRIM($D$18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23:E23">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>LEN(TRIM($D$23))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23:K23">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>LEN(TRIM($I$23))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24:E24">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>LEN(TRIM($D$24))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D25:E25">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>LEN(TRIM($D$25))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:E30">
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>LEN(TRIM($D$30))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D32:E32">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>LEN(TRIM($D$32))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="9">
     <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D19">
       <formula1>"Nueva,Usada"</formula1>
@@ -2264,10 +2393,15 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AL2"/>
+  <dimension ref="A1:AN2"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="38" max="38" width="9.10" style="0"/>
+    <col min="39" max="39" width="9.10" style="0"/>
+    <col min="40" max="40" width="9.10" style="0"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="3" customFormat="1">
+    <row r="1" spans="1:40" s="3" customFormat="1">
       <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
@@ -2382,8 +2516,14 @@
       <c r="AL1" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="2" spans="1:38">
+      <c r="AM1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AN1" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40">
       <c r="A2" t="str">
         <f>""</f>
         <v/>
@@ -2535,6 +2675,14 @@
       <c r="AL2" t="str">
         <f>IF(UPPER(Solicitud!D54)="SI","si",IF(UPPER(Solicitud!D54)="SÍ","si",""))</f>
         <v/>
+      </c>
+      <c r="AM2">
+        <f>Solicitud!F48</f>
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <f>Solicitud!I48</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
+++ b/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="107">
   <si>
     <t>SOLICITUD DE ASEGURAMIENTO DE MERCANCIA</t>
   </si>
@@ -32,36 +32,60 @@
     <t xml:space="preserve">Solicitante </t>
   </si>
   <si>
+    <t>Jose Perea</t>
+  </si>
+  <si>
     <t>Teléfono</t>
   </si>
   <si>
     <t>Fecha</t>
   </si>
   <si>
+    <t>24 petiembre 2026</t>
+  </si>
+  <si>
     <t>1. BENEFICIAROO DEL SEGURO</t>
   </si>
   <si>
     <t>Nombre</t>
   </si>
   <si>
+    <t>Patrick Perea</t>
+  </si>
+  <si>
     <t>Domicilio</t>
   </si>
   <si>
+    <t>Rancho del arco</t>
+  </si>
+  <si>
     <t>Contacto</t>
   </si>
   <si>
+    <t>abuela</t>
+  </si>
+  <si>
     <t>3. MERCANCIA POR ASEGURAR</t>
   </si>
   <si>
     <t>Mercancía asegurada</t>
   </si>
   <si>
+    <t>pantallas con IA</t>
+  </si>
+  <si>
     <t>Estado</t>
   </si>
   <si>
+    <t>Nueva</t>
+  </si>
+  <si>
     <t>Referencia</t>
   </si>
   <si>
+    <t>27 "</t>
+  </si>
+  <si>
     <t>4. RUTA Y TRANSPORTE</t>
   </si>
   <si>
@@ -71,24 +95,42 @@
     <t>Medio transporte</t>
   </si>
   <si>
+    <t>Marítimo</t>
+  </si>
+  <si>
     <t>Ciudad de origen</t>
   </si>
   <si>
+    <t>pekin</t>
+  </si>
+  <si>
     <t>País origen</t>
   </si>
   <si>
+    <t>china</t>
+  </si>
+  <si>
     <t>Ciudad de destino</t>
   </si>
   <si>
+    <t>cdmx</t>
+  </si>
+  <si>
     <t>País destino</t>
   </si>
   <si>
+    <t>mexico</t>
+  </si>
+  <si>
     <t>5.CONCEPTOS POR ASEGURAR</t>
   </si>
   <si>
     <t>Moneda</t>
   </si>
   <si>
+    <t>USD</t>
+  </si>
+  <si>
     <t>Valor factura</t>
   </si>
   <si>
@@ -107,15 +149,36 @@
     <t>6. DATOS DEL CONSIGNATARIO</t>
   </si>
   <si>
+    <t>pepe consignatario</t>
+  </si>
+  <si>
+    <t>xochimilco</t>
+  </si>
+  <si>
+    <t>Roberto lona</t>
+  </si>
+  <si>
     <t>7. DATOS DEL PROVEEDOR</t>
   </si>
   <si>
+    <t>xang pei</t>
+  </si>
+  <si>
+    <t>cerro de los remedios</t>
+  </si>
+  <si>
+    <t>tsao</t>
+  </si>
+  <si>
     <t>8.REFERENCIAS</t>
   </si>
   <si>
     <t>Terrestre</t>
   </si>
   <si>
+    <t>si</t>
+  </si>
+  <si>
     <t>Maritimo</t>
   </si>
   <si>
@@ -125,6 +188,9 @@
     <t>Talon embarque</t>
   </si>
   <si>
+    <t>ew34</t>
+  </si>
+  <si>
     <t>B/L</t>
   </si>
   <si>
@@ -137,10 +203,16 @@
     <t>Contenedor</t>
   </si>
   <si>
+    <t>we34</t>
+  </si>
+  <si>
     <t>Linea aerea</t>
   </si>
   <si>
     <t>9.DECLARACIÓN</t>
+  </si>
+  <si>
+    <t>SI</t>
   </si>
   <si>
     <t xml:space="preserve">Acepto que la información declarada es verídica </t>
@@ -300,8 +372,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -345,6 +417,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="12"/>
+      <color theme="2"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b val="1"/>
       <i val="0"/>
       <strike val="0"/>
@@ -361,16 +443,6 @@
       <u val="none"/>
       <sz val="11"/>
       <color rgb="FF262626"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="12"/>
-      <color theme="2"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -396,7 +468,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
+        <fgColor rgb="FFD6DCE4"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -408,13 +480,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6DCE4"/>
+        <fgColor rgb="FFDFEBF7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDFEBF7"/>
+        <fgColor rgb="FF0070C0"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -446,20 +518,9 @@
       <left style="thick">
         <color rgb="FFFFFFFF"/>
       </left>
-      <right/>
-      <top style="thick">
+      <right style="thick">
         <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right/>
+      </right>
       <top style="thick">
         <color rgb="FFFFFFFF"/>
       </top>
@@ -491,25 +552,34 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thick">
         <color rgb="FFFFFFFF"/>
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -526,10 +596,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
+      <left style="thick">
         <color rgb="FFFFFFFF"/>
-      </right>
+      </left>
+      <right/>
       <top style="thick">
         <color rgb="FFFFFFFF"/>
       </top>
@@ -537,18 +607,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thick">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFFFFFFF"/>
-      </left>
+      <left/>
       <right style="thick">
         <color rgb="FFFFFFFF"/>
       </right>
@@ -569,217 +628,195 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="55">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="5" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
       <protection locked="false"/>
     </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="5" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="true">
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-      <protection locked="true"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1239,7 +1276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:L63"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true" style="0"/>
     <col min="3" max="3" width="14.5" customWidth="true" style="0"/>
@@ -1249,81 +1286,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customHeight="1" ht="28">
-      <c r="A1" s="15"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="2"/>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" customHeight="1" ht="70">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="2"/>
+      <c r="A2" s="1"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="15"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="1"/>
+      <c r="B3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="2"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="15"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="2"/>
+      <c r="A4" s="1"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="1"/>
     </row>
     <row r="5" spans="1:12" customHeight="1" ht="34">
-      <c r="A5" s="15"/>
-      <c r="B5" s="18" t="s">
+      <c r="A5" s="1"/>
+      <c r="B5" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="2"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="1"/>
     </row>
     <row r="6" spans="1:12" customHeight="1" ht="23">
-      <c r="A6" s="15"/>
+      <c r="A6" s="1"/>
       <c r="B6" s="19" t="s">
         <v>2</v>
       </c>
@@ -1336,10 +1373,10 @@
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
       <c r="K6" s="19"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" customHeight="1" ht="6" s="1" customFormat="1">
-      <c r="A7" s="15"/>
+      <c r="L6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" customHeight="1" ht="6">
+      <c r="A7" s="1"/>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -1350,46 +1387,52 @@
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
       <c r="K7" s="20"/>
-      <c r="L7" s="2"/>
+      <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" customHeight="1" ht="23">
-      <c r="A8" s="15"/>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="21" t="s">
+      <c r="C8" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="21" t="s">
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="2"/>
+      <c r="G8" s="54">
+        <v>5530050231</v>
+      </c>
+      <c r="H8" s="47"/>
+      <c r="I8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="47"/>
+      <c r="L8" s="1"/>
     </row>
     <row r="9" spans="1:12" customHeight="1" ht="23">
-      <c r="A9" s="15"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="2"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12" customHeight="1" ht="23">
-      <c r="A10" s="15"/>
+      <c r="A10" s="1"/>
       <c r="B10" s="19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -1400,10 +1443,10 @@
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
-      <c r="L10" s="2"/>
+      <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:12" customHeight="1" ht="5">
-      <c r="A11" s="15"/>
+      <c r="A11" s="1"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
@@ -1414,88 +1457,94 @@
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
-      <c r="L11" s="2"/>
+      <c r="L11" s="1"/>
     </row>
     <row r="12" spans="1:12" customHeight="1" ht="23">
-      <c r="A12" s="15"/>
-      <c r="B12" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="2"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:12" customHeight="1" ht="23">
-      <c r="A13" s="15"/>
-      <c r="B13" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="2"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="1"/>
     </row>
     <row r="14" spans="1:12" customHeight="1" ht="23">
-      <c r="A14" s="15"/>
-      <c r="B14" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="2"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" customHeight="1" ht="23">
-      <c r="A15" s="15"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="2"/>
+      <c r="A15" s="1"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" customHeight="1" ht="23">
-      <c r="A16" s="15"/>
-      <c r="B16" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="2"/>
+      <c r="A16" s="1"/>
+      <c r="B16" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="50"/>
+      <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" customHeight="1" ht="5">
-      <c r="A17" s="15"/>
+      <c r="A17" s="1"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -1506,60 +1555,66 @@
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
       <c r="K17" s="20"/>
-      <c r="L17" s="2"/>
+      <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" customHeight="1" ht="23">
-      <c r="A18" s="15"/>
-      <c r="B18" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="2"/>
+      <c r="A18" s="1"/>
+      <c r="B18" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="21"/>
+      <c r="D18" s="48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" customHeight="1" ht="23">
-      <c r="A19" s="15"/>
-      <c r="B19" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="2"/>
+      <c r="A19" s="1"/>
+      <c r="B19" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="22"/>
+      <c r="D19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" customHeight="1" ht="23">
-      <c r="A20" s="15"/>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="2"/>
+      <c r="A20" s="1"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12" customHeight="1" ht="23">
-      <c r="A21" s="15"/>
+      <c r="A21" s="1"/>
       <c r="B21" s="19" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
@@ -1570,10 +1625,10 @@
       <c r="I21" s="19"/>
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
-      <c r="L21" s="2"/>
+      <c r="L21" s="1"/>
     </row>
     <row r="22" spans="1:12" customHeight="1" ht="5">
-      <c r="A22" s="15"/>
+      <c r="A22" s="1"/>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -1584,80 +1639,92 @@
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
       <c r="K22" s="20"/>
-      <c r="L22" s="2"/>
+      <c r="L22" s="1"/>
     </row>
     <row r="23" spans="1:12" customHeight="1" ht="23">
-      <c r="A23" s="15"/>
-      <c r="B23" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="45"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="2"/>
+      <c r="A23" s="1"/>
+      <c r="B23" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="46">
+        <v>46289</v>
+      </c>
+      <c r="E23" s="47"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="42"/>
+      <c r="I23" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="40"/>
+      <c r="K23" s="40"/>
+      <c r="L23" s="1"/>
     </row>
     <row r="24" spans="1:12" customHeight="1" ht="23">
-      <c r="A24" s="15"/>
-      <c r="B24" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="45"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="49"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="2"/>
+      <c r="A24" s="1"/>
+      <c r="B24" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="38"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="H24" s="42"/>
+      <c r="I24" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="J24" s="43"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="1"/>
     </row>
     <row r="25" spans="1:12" customHeight="1" ht="23">
-      <c r="A25" s="15"/>
-      <c r="B25" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="46"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="2"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="45"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="35"/>
+      <c r="I25" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="1"/>
     </row>
     <row r="26" spans="1:12" customHeight="1" ht="23">
-      <c r="A26" s="15"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="2"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="1"/>
     </row>
     <row r="27" spans="1:12" customHeight="1" ht="23">
-      <c r="A27" s="15"/>
+      <c r="A27" s="1"/>
       <c r="B27" s="19" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -1668,10 +1735,10 @@
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
-      <c r="L27" s="2"/>
+      <c r="L27" s="1"/>
     </row>
     <row r="28" spans="1:12" customHeight="1" ht="5">
-      <c r="A28" s="15"/>
+      <c r="A28" s="1"/>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -1682,94 +1749,106 @@
       <c r="I28" s="20"/>
       <c r="J28" s="20"/>
       <c r="K28" s="20"/>
-      <c r="L28" s="2"/>
+      <c r="L28" s="1"/>
     </row>
     <row r="29" spans="1:12" customHeight="1" ht="23">
-      <c r="A29" s="15"/>
-      <c r="B29" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="2"/>
+      <c r="A29" s="1"/>
+      <c r="B29" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="11"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="1"/>
     </row>
     <row r="30" spans="1:12" customHeight="1" ht="23">
-      <c r="A30" s="15"/>
-      <c r="B30" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="45"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="2"/>
+      <c r="A30" s="1"/>
+      <c r="B30" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="37">
+        <v>3000</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="H30" s="42"/>
+      <c r="I30" s="37">
+        <v>0</v>
+      </c>
+      <c r="J30" s="43"/>
+      <c r="K30" s="38"/>
+      <c r="L30" s="1"/>
     </row>
     <row r="31" spans="1:12" customHeight="1" ht="23">
-      <c r="A31" s="15"/>
-      <c r="B31" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="41"/>
-      <c r="G31" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="46"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
-      <c r="L31" s="2"/>
+      <c r="A31" s="1"/>
+      <c r="B31" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="22"/>
+      <c r="D31" s="37">
+        <v>0</v>
+      </c>
+      <c r="E31" s="38"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" s="35"/>
+      <c r="I31" s="39">
+        <v>0</v>
+      </c>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="1"/>
     </row>
     <row r="32" spans="1:12" customHeight="1" ht="23">
-      <c r="A32" s="15"/>
-      <c r="B32" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
-      <c r="L32" s="2"/>
+      <c r="A32" s="1"/>
+      <c r="B32" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="22"/>
+      <c r="D32" s="37">
+        <v>3000</v>
+      </c>
+      <c r="E32" s="38"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="1"/>
     </row>
     <row r="33" spans="1:12" customHeight="1" ht="23">
-      <c r="A33" s="15"/>
-      <c r="B33" s="22"/>
-      <c r="C33" s="22"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="2"/>
+      <c r="A33" s="1"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" customHeight="1" ht="23">
-      <c r="A34" s="15"/>
+      <c r="A34" s="1"/>
       <c r="B34" s="19" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
@@ -1780,10 +1859,10 @@
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
-      <c r="L34" s="2"/>
+      <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" customHeight="1" ht="5">
-      <c r="A35" s="15"/>
+      <c r="A35" s="1"/>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
       <c r="D35" s="20"/>
@@ -1794,74 +1873,80 @@
       <c r="I35" s="20"/>
       <c r="J35" s="20"/>
       <c r="K35" s="20"/>
-      <c r="L35" s="2"/>
+      <c r="L35" s="1"/>
     </row>
     <row r="36" spans="1:12" customHeight="1" ht="23">
-      <c r="A36" s="15"/>
-      <c r="B36" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="7"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="31"/>
-      <c r="G36" s="31"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="51"/>
-      <c r="L36" s="2"/>
+      <c r="A36" s="1"/>
+      <c r="B36" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="33"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="1"/>
     </row>
     <row r="37" spans="1:12" customHeight="1" ht="23">
-      <c r="A37" s="15"/>
-      <c r="B37" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="7"/>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="2"/>
+      <c r="A37" s="1"/>
+      <c r="B37" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="33"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="7"/>
+      <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" customHeight="1" ht="23">
-      <c r="A38" s="15"/>
-      <c r="B38" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="7"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="2"/>
+      <c r="A38" s="1"/>
+      <c r="B38" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="1"/>
     </row>
     <row r="39" spans="1:12" customHeight="1" ht="23">
-      <c r="A39" s="15"/>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="2"/>
+      <c r="A39" s="1"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="1"/>
     </row>
     <row r="40" spans="1:12" customHeight="1" ht="23">
-      <c r="A40" s="15"/>
+      <c r="A40" s="1"/>
       <c r="B40" s="19" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="19"/>
@@ -1872,10 +1957,10 @@
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
-      <c r="L40" s="2"/>
+      <c r="L40" s="1"/>
     </row>
     <row r="41" spans="1:12" customHeight="1" ht="5">
-      <c r="A41" s="15"/>
+      <c r="A41" s="1"/>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
@@ -1886,74 +1971,80 @@
       <c r="I41" s="20"/>
       <c r="J41" s="20"/>
       <c r="K41" s="20"/>
-      <c r="L41" s="2"/>
+      <c r="L41" s="1"/>
     </row>
     <row r="42" spans="1:12" customHeight="1" ht="23">
-      <c r="A42" s="15"/>
-      <c r="B42" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="51"/>
-      <c r="L42" s="2"/>
+      <c r="A42" s="1"/>
+      <c r="B42" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="15"/>
+      <c r="L42" s="1"/>
     </row>
     <row r="43" spans="1:12" customHeight="1" ht="23">
-      <c r="A43" s="15"/>
-      <c r="B43" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="31"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="31"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="2"/>
+      <c r="A43" s="1"/>
+      <c r="B43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="1"/>
     </row>
     <row r="44" spans="1:12" customHeight="1" ht="23">
-      <c r="A44" s="15"/>
-      <c r="B44" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="2"/>
+      <c r="A44" s="1"/>
+      <c r="B44" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="33"/>
+      <c r="E44" s="33"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="1"/>
     </row>
     <row r="45" spans="1:12" customHeight="1" ht="23">
-      <c r="A45" s="15"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="22"/>
-      <c r="L45" s="2"/>
+      <c r="A45" s="1"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="7"/>
+      <c r="L45" s="1"/>
     </row>
     <row r="46" spans="1:12" customHeight="1" ht="23">
-      <c r="A46" s="15"/>
+      <c r="A46" s="1"/>
       <c r="B46" s="19" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C46" s="19"/>
       <c r="D46" s="19"/>
@@ -1964,10 +2055,10 @@
       <c r="I46" s="19"/>
       <c r="J46" s="19"/>
       <c r="K46" s="19"/>
-      <c r="L46" s="2"/>
+      <c r="L46" s="1"/>
     </row>
     <row r="47" spans="1:12" customHeight="1" ht="5">
-      <c r="A47" s="15"/>
+      <c r="A47" s="1"/>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
@@ -1978,86 +2069,104 @@
       <c r="I47" s="20"/>
       <c r="J47" s="20"/>
       <c r="K47" s="20"/>
-      <c r="L47" s="2"/>
+      <c r="L47" s="1"/>
     </row>
     <row r="48" spans="1:12" customHeight="1" ht="23">
-      <c r="A48" s="15"/>
-      <c r="B48" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="8"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="F48" s="8"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="50"/>
-      <c r="K48" s="32"/>
-      <c r="L48" s="2"/>
+      <c r="A48" s="1"/>
+      <c r="B48" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D48" s="27"/>
+      <c r="E48" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G48" s="27"/>
+      <c r="H48" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="I48" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="J48" s="29"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="1"/>
     </row>
     <row r="49" spans="1:12" customHeight="1" ht="23">
-      <c r="A49" s="15"/>
-      <c r="B49" s="25" t="s">
+      <c r="A49" s="1"/>
+      <c r="B49" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" s="31"/>
+      <c r="D49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="F49" s="26">
+        <v>234</v>
+      </c>
+      <c r="G49" s="27"/>
+      <c r="H49" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="I49" s="28">
+        <v>3445</v>
+      </c>
+      <c r="J49" s="29"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="1"/>
+    </row>
+    <row r="50" spans="1:12" customHeight="1" ht="23">
+      <c r="A50" s="1"/>
+      <c r="B50" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="31"/>
+      <c r="D50" s="16">
         <v>34</v>
       </c>
-      <c r="C49" s="54"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="F49" s="8"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="I49" s="9"/>
-      <c r="J49" s="50"/>
-      <c r="K49" s="32"/>
-      <c r="L49" s="2"/>
-    </row>
-    <row r="50" spans="1:12" customHeight="1" ht="23">
-      <c r="A50" s="15"/>
-      <c r="B50" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" s="54"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="50"/>
-      <c r="K50" s="32"/>
-      <c r="L50" s="2"/>
+      <c r="E50" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F50" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G50" s="27"/>
+      <c r="H50" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="I50" s="28">
+        <v>43355</v>
+      </c>
+      <c r="J50" s="29"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="1"/>
     </row>
     <row r="51" spans="1:12" customHeight="1" ht="23">
-      <c r="A51" s="15"/>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="15"/>
-      <c r="L51" s="2"/>
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
     </row>
     <row r="52" spans="1:12" customHeight="1" ht="23">
-      <c r="A52" s="15"/>
+      <c r="A52" s="1"/>
       <c r="B52" s="19" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C52" s="19"/>
       <c r="D52" s="19"/>
@@ -2068,10 +2177,10 @@
       <c r="I52" s="19"/>
       <c r="J52" s="19"/>
       <c r="K52" s="19"/>
-      <c r="L52" s="2"/>
+      <c r="L52" s="1"/>
     </row>
     <row r="53" spans="1:12" customHeight="1" ht="5">
-      <c r="A53" s="15"/>
+      <c r="A53" s="1"/>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
@@ -2082,211 +2191,172 @@
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
       <c r="K53" s="20"/>
-      <c r="L53" s="2"/>
+      <c r="L53" s="1"/>
     </row>
     <row r="54" spans="1:12" customHeight="1" ht="23">
-      <c r="A54" s="15"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="F54" s="42"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="42"/>
-      <c r="I54" s="42"/>
-      <c r="J54" s="42"/>
-      <c r="K54" s="52"/>
-      <c r="L54" s="2"/>
+      <c r="A54" s="1"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="1"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="15"/>
-      <c r="B55" s="15"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
-      <c r="K55" s="15"/>
-      <c r="L55" s="2"/>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="15"/>
-      <c r="B56" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="27"/>
-      <c r="K56" s="27"/>
-      <c r="L56" s="2"/>
+      <c r="A56" s="1"/>
+      <c r="B56" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="18"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="18"/>
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="1"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="15"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
-      <c r="L57" s="2"/>
+      <c r="A57" s="1"/>
+      <c r="B57" s="18"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="18"/>
+      <c r="F57" s="18"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="18"/>
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="1"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="15"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="2"/>
+      <c r="A58" s="1"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="18"/>
+      <c r="H58" s="18"/>
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="1"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="15"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
-      <c r="L59" s="2"/>
+      <c r="A59" s="1"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="18"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="18"/>
+      <c r="H59" s="18"/>
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="18"/>
+      <c r="L59" s="1"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="15"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="2"/>
+      <c r="A60" s="1"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="18"/>
+      <c r="H60" s="18"/>
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="18"/>
+      <c r="L60" s="1"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-      <c r="L61" s="2"/>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-      <c r="L62" s="2"/>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="2"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection password="9328" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" deleteColumns="1" deleteRows="1" sort="1" selectLockedCells="0" selectUnlockedCells="0"/>
+  <sheetProtection password="9328" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells>
-    <mergeCell ref="B56:K60"/>
-    <mergeCell ref="B52:K52"/>
-    <mergeCell ref="B53:K53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="E54:K54"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="B46:K46"/>
-    <mergeCell ref="B47:K47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="C38:J38"/>
-    <mergeCell ref="B40:K40"/>
-    <mergeCell ref="B41:K41"/>
-    <mergeCell ref="C42:J42"/>
-    <mergeCell ref="C43:J43"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="B34:K34"/>
-    <mergeCell ref="B35:K35"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="C37:J37"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="B27:K27"/>
-    <mergeCell ref="B28:K28"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B3:K4"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
     <mergeCell ref="G23:H23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
     <mergeCell ref="I23:K23"/>
     <mergeCell ref="B21:K21"/>
     <mergeCell ref="B22:K22"/>
@@ -2296,16 +2366,57 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B16:K16"/>
     <mergeCell ref="B17:K17"/>
-    <mergeCell ref="B10:K10"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="B11:K11"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B3:K4"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B27:K27"/>
+    <mergeCell ref="B28:K28"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="B34:K34"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="C38:J38"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="B41:K41"/>
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="C43:J43"/>
+    <mergeCell ref="B46:K46"/>
+    <mergeCell ref="B47:K47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="B56:K60"/>
+    <mergeCell ref="B52:K52"/>
+    <mergeCell ref="B53:K53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="E54:K54"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:E8">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2317,73 +2428,69 @@
       <formula>LEN(TRIM($C$12))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:K18">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>LEN(TRIM($D$18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D23:E23">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>LEN(TRIM($D$23))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I23:K23">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>LEN(TRIM($I$23))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D24:E24">
-    <cfRule type="expression" dxfId="5" priority="6">
+    <cfRule type="expression" dxfId="3" priority="6">
       <formula>LEN(TRIM($D$24))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D25:E25">
-    <cfRule type="expression" dxfId="6" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>LEN(TRIM($D$25))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="7" priority="8">
+    <cfRule type="expression" dxfId="5" priority="8">
       <formula>LEN(TRIM($D$30))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32:E32">
-    <cfRule type="expression" dxfId="8" priority="9">
+    <cfRule type="expression" dxfId="6" priority="9">
       <formula>LEN(TRIM($D$32))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="9">
-    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D19">
+  <conditionalFormatting sqref="D18:K18">
+    <cfRule type="expression" dxfId="7" priority="3">
+      <formula>LEN(TRIM($D$18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I23:K23">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>LEN(TRIM($I$23))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="7">
+    <dataValidation type="list" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D19">
       <formula1>"Nueva,Usada"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D29">
+    <dataValidation type="list" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D29">
       <formula1>"USD,PESOS"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D54">
+    <dataValidation type="list" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D54">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="I23">
+    <dataValidation type="list" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="I23">
       <formula1>"Terrestre,Marítimo,Aéreo,Multimodal"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D30">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D30:D32 I30:I31">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="I30">
-      <formula1>0</formula1>
+    <dataValidation type="date" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Escribe una fecha real, por ejemplo 24/09/2026. Si tu Excel no la acepta así, escríbela con el formato de fecha de tu computadora." promptTitle="Fecha" prompt="Escribe la fecha, por ejemplo 24/09/2026." sqref="J8:K8">
+      <formula1>DATE(2000,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D31">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="I31">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D32">
-      <formula1>0</formula1>
+    <dataValidation type="date" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Escribe una fecha real, por ejemplo 24/09/2026. Si tu Excel no la acepta así, escríbela con el formato de fecha de tu computadora." promptTitle="Fecha" prompt="Escribe la fecha, por ejemplo 24/09/2026." sqref="D23:E23">
+      <formula1>DATE(2000,1,1)</formula1>
+      <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2394,133 +2501,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AN2"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="38" max="38" width="9.10" style="0"/>
-    <col min="39" max="39" width="9.10" style="0"/>
-    <col min="40" max="40" width="9.10" style="0"/>
+    <col min="38" max="38" width="9.1640625" customWidth="true" style="0"/>
+    <col min="39" max="39" width="9.1640625" customWidth="true" style="0"/>
+    <col min="40" max="40" width="9.1640625" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="3" customFormat="1">
-      <c r="A1" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y1" s="3" t="s">
+    <row r="1" spans="1:40" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>82</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN1" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:40">
@@ -2536,73 +2643,73 @@
         <f>"Constancia"</f>
         <v>Constancia</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="str">
         <f>Solicitud!C8</f>
-        <v>0</v>
+        <v>Jose Perea</v>
       </c>
       <c r="E2">
         <f>Solicitud!G8</f>
-        <v>0</v>
-      </c>
-      <c r="F2">
+        <v>5530050231</v>
+      </c>
+      <c r="F2" t="str">
         <f>Solicitud!J8</f>
-        <v>0</v>
-      </c>
-      <c r="G2">
+        <v>24 petiembre 2026</v>
+      </c>
+      <c r="G2" t="str">
         <f>Solicitud!C12</f>
-        <v>0</v>
-      </c>
-      <c r="H2">
+        <v>Patrick Perea</v>
+      </c>
+      <c r="H2" t="str">
         <f>Solicitud!C13</f>
-        <v>0</v>
-      </c>
-      <c r="I2">
+        <v>Rancho del arco</v>
+      </c>
+      <c r="I2" t="str">
         <f>Solicitud!C14</f>
-        <v>0</v>
-      </c>
-      <c r="J2">
+        <v>abuela</v>
+      </c>
+      <c r="J2" t="str">
         <f>Solicitud!D19</f>
-        <v>0</v>
-      </c>
-      <c r="K2">
+        <v>Nueva</v>
+      </c>
+      <c r="K2" t="str">
         <f>Solicitud!D18</f>
-        <v>0</v>
-      </c>
-      <c r="L2">
+        <v>pantallas con IA</v>
+      </c>
+      <c r="L2" t="str">
         <f>Solicitud!F19</f>
-        <v>0</v>
+        <v>27 "</v>
       </c>
       <c r="M2">
         <f>Solicitud!D23</f>
-        <v>0</v>
-      </c>
-      <c r="N2">
+        <v>46289</v>
+      </c>
+      <c r="N2" t="str">
         <f>Solicitud!D24</f>
-        <v>0</v>
-      </c>
-      <c r="O2">
+        <v>pekin</v>
+      </c>
+      <c r="O2" t="str">
         <f>Solicitud!I24</f>
-        <v>0</v>
-      </c>
-      <c r="P2">
+        <v>china</v>
+      </c>
+      <c r="P2" t="str">
         <f>Solicitud!D25</f>
-        <v>0</v>
-      </c>
-      <c r="Q2">
+        <v>cdmx</v>
+      </c>
+      <c r="Q2" t="str">
         <f>Solicitud!I25</f>
-        <v>0</v>
-      </c>
-      <c r="R2">
+        <v>mexico</v>
+      </c>
+      <c r="R2" t="str">
         <f>Solicitud!I23</f>
-        <v>0</v>
-      </c>
-      <c r="S2">
+        <v>Marítimo</v>
+      </c>
+      <c r="S2" t="str">
         <f>IF(OR(UPPER(Solicitud!D29)="MXN",UPPER(Solicitud!D29)="PESOS"),"pesos",IF(UPPER(Solicitud!D29)="USD","usd",Solicitud!D29))</f>
-        <v>0</v>
+        <v>usd</v>
       </c>
       <c r="T2">
         <f>Solicitud!D30</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="U2">
         <f>Solicitud!I30</f>
@@ -2618,77 +2725,77 @@
       </c>
       <c r="X2">
         <f>Solicitud!D32</f>
-        <v>0</v>
-      </c>
-      <c r="Y2">
+        <v>3000</v>
+      </c>
+      <c r="Y2" t="str">
         <f>Solicitud!C36</f>
-        <v>0</v>
-      </c>
-      <c r="Z2">
+        <v>pepe consignatario</v>
+      </c>
+      <c r="Z2" t="str">
         <f>Solicitud!C37</f>
-        <v>0</v>
-      </c>
-      <c r="AA2">
+        <v>xochimilco</v>
+      </c>
+      <c r="AA2" t="str">
         <f>Solicitud!C38</f>
-        <v>0</v>
-      </c>
-      <c r="AB2">
+        <v>Roberto lona</v>
+      </c>
+      <c r="AB2" t="str">
         <f>Solicitud!C42</f>
-        <v>0</v>
-      </c>
-      <c r="AC2">
+        <v>xang pei</v>
+      </c>
+      <c r="AC2" t="str">
         <f>Solicitud!C43</f>
-        <v>0</v>
-      </c>
-      <c r="AD2">
+        <v>cerro de los remedios</v>
+      </c>
+      <c r="AD2" t="str">
         <f>Solicitud!C44</f>
-        <v>0</v>
-      </c>
-      <c r="AE2">
+        <v>tsao</v>
+      </c>
+      <c r="AE2" t="str">
         <f>Solicitud!C48</f>
-        <v>0</v>
-      </c>
-      <c r="AF2">
+        <v>si</v>
+      </c>
+      <c r="AF2" t="str">
         <f>Solicitud!D49</f>
-        <v>0</v>
+        <v>ew34</v>
       </c>
       <c r="AG2">
         <f>Solicitud!D50</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH2">
         <f>Solicitud!F49</f>
-        <v>0</v>
-      </c>
-      <c r="AI2">
+        <v>234</v>
+      </c>
+      <c r="AI2" t="str">
         <f>Solicitud!F50</f>
-        <v>0</v>
+        <v>we34</v>
       </c>
       <c r="AJ2">
         <f>Solicitud!I49</f>
-        <v>0</v>
+        <v>3445</v>
       </c>
       <c r="AK2">
         <f>Solicitud!I50</f>
-        <v>0</v>
+        <v>43355</v>
       </c>
       <c r="AL2" t="str">
         <f>IF(UPPER(Solicitud!D54)="SI","si",IF(UPPER(Solicitud!D54)="SÍ","si",""))</f>
-        <v/>
-      </c>
-      <c r="AM2">
+        <v>si</v>
+      </c>
+      <c r="AM2" t="str">
         <f>Solicitud!F48</f>
-        <v>0</v>
-      </c>
-      <c r="AN2">
+        <v>si</v>
+      </c>
+      <c r="AN2" t="str">
         <f>Solicitud!I48</f>
-        <v>0</v>
+        <v>si</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection password="9328" sheet="1"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
--- a/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
+++ b/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
   <si>
     <t>SOLICITUD DE ASEGURAMIENTO DE MERCANCIA</t>
   </si>
@@ -32,60 +32,36 @@
     <t xml:space="preserve">Solicitante </t>
   </si>
   <si>
-    <t>Jose Perea</t>
-  </si>
-  <si>
     <t>Teléfono</t>
   </si>
   <si>
     <t>Fecha</t>
   </si>
   <si>
-    <t>24 petiembre 2026</t>
-  </si>
-  <si>
     <t>1. BENEFICIAROO DEL SEGURO</t>
   </si>
   <si>
     <t>Nombre</t>
   </si>
   <si>
-    <t>Patrick Perea</t>
-  </si>
-  <si>
     <t>Domicilio</t>
   </si>
   <si>
-    <t>Rancho del arco</t>
-  </si>
-  <si>
     <t>Contacto</t>
   </si>
   <si>
-    <t>abuela</t>
-  </si>
-  <si>
     <t>3. MERCANCIA POR ASEGURAR</t>
   </si>
   <si>
     <t>Mercancía asegurada</t>
   </si>
   <si>
-    <t>pantallas con IA</t>
-  </si>
-  <si>
     <t>Estado</t>
   </si>
   <si>
-    <t>Nueva</t>
-  </si>
-  <si>
     <t>Referencia</t>
   </si>
   <si>
-    <t>27 "</t>
-  </si>
-  <si>
     <t>4. RUTA Y TRANSPORTE</t>
   </si>
   <si>
@@ -95,42 +71,24 @@
     <t>Medio transporte</t>
   </si>
   <si>
-    <t>Marítimo</t>
-  </si>
-  <si>
     <t>Ciudad de origen</t>
   </si>
   <si>
-    <t>pekin</t>
-  </si>
-  <si>
     <t>País origen</t>
   </si>
   <si>
-    <t>china</t>
-  </si>
-  <si>
     <t>Ciudad de destino</t>
   </si>
   <si>
-    <t>cdmx</t>
-  </si>
-  <si>
     <t>País destino</t>
   </si>
   <si>
-    <t>mexico</t>
-  </si>
-  <si>
     <t>5.CONCEPTOS POR ASEGURAR</t>
   </si>
   <si>
     <t>Moneda</t>
   </si>
   <si>
-    <t>USD</t>
-  </si>
-  <si>
     <t>Valor factura</t>
   </si>
   <si>
@@ -149,36 +107,15 @@
     <t>6. DATOS DEL CONSIGNATARIO</t>
   </si>
   <si>
-    <t>pepe consignatario</t>
-  </si>
-  <si>
-    <t>xochimilco</t>
-  </si>
-  <si>
-    <t>Roberto lona</t>
-  </si>
-  <si>
     <t>7. DATOS DEL PROVEEDOR</t>
   </si>
   <si>
-    <t>xang pei</t>
-  </si>
-  <si>
-    <t>cerro de los remedios</t>
-  </si>
-  <si>
-    <t>tsao</t>
-  </si>
-  <si>
     <t>8.REFERENCIAS</t>
   </si>
   <si>
     <t>Terrestre</t>
   </si>
   <si>
-    <t>si</t>
-  </si>
-  <si>
     <t>Maritimo</t>
   </si>
   <si>
@@ -188,9 +125,6 @@
     <t>Talon embarque</t>
   </si>
   <si>
-    <t>ew34</t>
-  </si>
-  <si>
     <t>B/L</t>
   </si>
   <si>
@@ -203,16 +137,10 @@
     <t>Contenedor</t>
   </si>
   <si>
-    <t>we34</t>
-  </si>
-  <si>
     <t>Linea aerea</t>
   </si>
   <si>
     <t>9.DECLARACIÓN</t>
-  </si>
-  <si>
-    <t>SI</t>
   </si>
   <si>
     <t xml:space="preserve">Acepto que la información declarada es verídica </t>
@@ -372,8 +300,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -417,16 +345,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="12"/>
-      <color theme="2"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b val="1"/>
       <i val="0"/>
       <strike val="0"/>
@@ -443,6 +361,16 @@
       <u val="none"/>
       <sz val="11"/>
       <color rgb="FF262626"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="12"/>
+      <color theme="2"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
@@ -468,7 +396,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD6DCE4"/>
+        <fgColor rgb="FF0070C0"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -480,13 +408,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDFEBF7"/>
+        <fgColor rgb="FFD6DCE4"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
+        <fgColor rgb="FFDFEBF7"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -518,9 +446,20 @@
       <left style="thick">
         <color rgb="FFFFFFFF"/>
       </left>
-      <right style="thick">
+      <right/>
+      <top style="thick">
         <color rgb="FFFFFFFF"/>
-      </right>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right/>
       <top style="thick">
         <color rgb="FFFFFFFF"/>
       </top>
@@ -552,11 +491,48 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thick">
         <color rgb="FFFFFFFF"/>
       </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="thick">
+        <color rgb="FFFFFFFF"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -573,41 +549,6 @@
       <left style="thick">
         <color rgb="FFFFFFFF"/>
       </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thick">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thick">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thick">
         <color rgb="FFFFFFFF"/>
       </right>
@@ -628,27 +569,23 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="55">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
     <xf xfId="0" fontId="2" numFmtId="14" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
@@ -657,166 +594,192 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
       <protection locked="false"/>
     </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
     <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="true">
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="4" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="5" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="6" numFmtId="0" fillId="5" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="7" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
+      <protection locked="true"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="5" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="2" borderId="4" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="6" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="5" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="2"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="7" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="164" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="2" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="11" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="10" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="165" fillId="3" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-      <protection locked="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="6" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
-    <xf xfId="0" fontId="4" numFmtId="0" fillId="5" borderId="12" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="5" numFmtId="0" fillId="7" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="6" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-      <protection locked="false"/>
+      <protection locked="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1276,7 +1239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:L63"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true" style="0"/>
     <col min="3" max="3" width="14.5" customWidth="true" style="0"/>
@@ -1286,81 +1249,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" customHeight="1" ht="28">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" spans="1:12" customHeight="1" ht="70">
-      <c r="A2" s="1"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="1"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="2"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="1"/>
-      <c r="B3" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="1"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="1"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="1"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" customHeight="1" ht="34">
-      <c r="A5" s="1"/>
-      <c r="B5" s="53" t="s">
+      <c r="A5" s="15"/>
+      <c r="B5" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="1"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:12" customHeight="1" ht="23">
-      <c r="A6" s="1"/>
+      <c r="A6" s="15"/>
       <c r="B6" s="19" t="s">
         <v>2</v>
       </c>
@@ -1373,10 +1336,10 @@
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
       <c r="K6" s="19"/>
-      <c r="L6" s="1"/>
-    </row>
-    <row r="7" spans="1:12" customHeight="1" ht="6">
-      <c r="A7" s="1"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:12" customHeight="1" ht="6" s="1" customFormat="1">
+      <c r="A7" s="15"/>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -1387,52 +1350,46 @@
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
       <c r="K7" s="20"/>
-      <c r="L7" s="1"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" spans="1:12" customHeight="1" ht="23">
-      <c r="A8" s="1"/>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="15"/>
+      <c r="B8" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="4"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="5"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="54">
-        <v>5530050231</v>
-      </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="6" t="s">
+      <c r="J8" s="12"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:12" customHeight="1" ht="23">
+      <c r="A9" s="15"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:12" customHeight="1" ht="23">
+      <c r="A10" s="15"/>
+      <c r="B10" s="19" t="s">
         <v>6</v>
-      </c>
-      <c r="J8" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="1"/>
-    </row>
-    <row r="9" spans="1:12" customHeight="1" ht="23">
-      <c r="A9" s="1"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="1"/>
-    </row>
-    <row r="10" spans="1:12" customHeight="1" ht="23">
-      <c r="A10" s="1"/>
-      <c r="B10" s="19" t="s">
-        <v>8</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -1443,10 +1400,10 @@
       <c r="I10" s="19"/>
       <c r="J10" s="19"/>
       <c r="K10" s="19"/>
-      <c r="L10" s="1"/>
+      <c r="L10" s="2"/>
     </row>
     <row r="11" spans="1:12" customHeight="1" ht="5">
-      <c r="A11" s="1"/>
+      <c r="A11" s="15"/>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
       <c r="D11" s="20"/>
@@ -1457,94 +1414,88 @@
       <c r="I11" s="20"/>
       <c r="J11" s="20"/>
       <c r="K11" s="20"/>
-      <c r="L11" s="1"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" spans="1:12" customHeight="1" ht="23">
-      <c r="A12" s="1"/>
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12" customHeight="1" ht="23">
+      <c r="A13" s="15"/>
+      <c r="B13" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12" customHeight="1" ht="23">
+      <c r="A14" s="15"/>
+      <c r="B14" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" customHeight="1" ht="23">
+      <c r="A15" s="15"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" customHeight="1" ht="23">
+      <c r="A16" s="15"/>
+      <c r="B16" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="33"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="1"/>
-    </row>
-    <row r="13" spans="1:12" customHeight="1" ht="23">
-      <c r="A13" s="1"/>
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:12" customHeight="1" ht="23">
-      <c r="A14" s="1"/>
-      <c r="B14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:12" customHeight="1" ht="23">
-      <c r="A15" s="1"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:12" customHeight="1" ht="23">
-      <c r="A16" s="1"/>
-      <c r="B16" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="1"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12" customHeight="1" ht="5">
-      <c r="A17" s="1"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -1555,66 +1506,60 @@
       <c r="I17" s="20"/>
       <c r="J17" s="20"/>
       <c r="K17" s="20"/>
-      <c r="L17" s="1"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12" customHeight="1" ht="23">
-      <c r="A18" s="1"/>
-      <c r="B18" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="48" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="49"/>
-      <c r="K18" s="49"/>
-      <c r="L18" s="1"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" customHeight="1" ht="23">
-      <c r="A19" s="1"/>
-      <c r="B19" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="22"/>
-      <c r="D19" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="1"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="28"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" customHeight="1" ht="23">
-      <c r="A20" s="1"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="1"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" customHeight="1" ht="23">
-      <c r="A21" s="1"/>
+      <c r="A21" s="15"/>
       <c r="B21" s="19" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
@@ -1625,10 +1570,10 @@
       <c r="I21" s="19"/>
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
-      <c r="L21" s="1"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" customHeight="1" ht="5">
-      <c r="A22" s="1"/>
+      <c r="A22" s="15"/>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -1639,92 +1584,80 @@
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
       <c r="K22" s="20"/>
-      <c r="L22" s="1"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" customHeight="1" ht="23">
-      <c r="A23" s="1"/>
-      <c r="B23" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="46">
-        <v>46289</v>
-      </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="H23" s="42"/>
-      <c r="I23" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J23" s="40"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="1"/>
+      <c r="A23" s="15"/>
+      <c r="B23" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="45"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" customHeight="1" ht="23">
-      <c r="A24" s="1"/>
-      <c r="B24" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="E24" s="38"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" s="42"/>
-      <c r="I24" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="J24" s="43"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="1"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="45"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" customHeight="1" ht="23">
-      <c r="A25" s="1"/>
-      <c r="B25" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="45"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="H25" s="35"/>
-      <c r="I25" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="1"/>
+      <c r="A25" s="15"/>
+      <c r="B25" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="46"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" customHeight="1" ht="23">
-      <c r="A26" s="1"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="1"/>
+      <c r="A26" s="15"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="2"/>
     </row>
     <row r="27" spans="1:12" customHeight="1" ht="23">
-      <c r="A27" s="1"/>
+      <c r="A27" s="15"/>
       <c r="B27" s="19" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
@@ -1735,10 +1668,10 @@
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
-      <c r="L27" s="1"/>
+      <c r="L27" s="2"/>
     </row>
     <row r="28" spans="1:12" customHeight="1" ht="5">
-      <c r="A28" s="1"/>
+      <c r="A28" s="15"/>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="20"/>
@@ -1749,106 +1682,94 @@
       <c r="I28" s="20"/>
       <c r="J28" s="20"/>
       <c r="K28" s="20"/>
-      <c r="L28" s="1"/>
+      <c r="L28" s="2"/>
     </row>
     <row r="29" spans="1:12" customHeight="1" ht="23">
-      <c r="A29" s="1"/>
-      <c r="B29" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="1"/>
+      <c r="A29" s="15"/>
+      <c r="B29" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="28"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="45"/>
+      <c r="I29" s="47"/>
+      <c r="J29" s="47"/>
+      <c r="K29" s="47"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" customHeight="1" ht="23">
-      <c r="A30" s="1"/>
-      <c r="B30" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="37">
-        <v>3000</v>
-      </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="H30" s="42"/>
-      <c r="I30" s="37">
-        <v>0</v>
-      </c>
-      <c r="J30" s="43"/>
-      <c r="K30" s="38"/>
-      <c r="L30" s="1"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="45"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" customHeight="1" ht="23">
-      <c r="A31" s="1"/>
-      <c r="B31" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="37">
-        <v>0</v>
-      </c>
-      <c r="E31" s="38"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="H31" s="35"/>
-      <c r="I31" s="39">
-        <v>0</v>
-      </c>
-      <c r="J31" s="40"/>
-      <c r="K31" s="40"/>
-      <c r="L31" s="1"/>
+      <c r="A31" s="15"/>
+      <c r="B31" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" s="28"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="46"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" customHeight="1" ht="23">
-      <c r="A32" s="1"/>
-      <c r="B32" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="22"/>
-      <c r="D32" s="37">
-        <v>3000</v>
-      </c>
-      <c r="E32" s="38"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="1"/>
+      <c r="A32" s="15"/>
+      <c r="B32" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="28"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="47"/>
+      <c r="J32" s="47"/>
+      <c r="K32" s="47"/>
+      <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" customHeight="1" ht="23">
-      <c r="A33" s="1"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="1"/>
+      <c r="A33" s="15"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" customHeight="1" ht="23">
-      <c r="A34" s="1"/>
+      <c r="A34" s="15"/>
       <c r="B34" s="19" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C34" s="19"/>
       <c r="D34" s="19"/>
@@ -1859,10 +1780,10 @@
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
-      <c r="L34" s="1"/>
+      <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" customHeight="1" ht="5">
-      <c r="A35" s="1"/>
+      <c r="A35" s="15"/>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
       <c r="D35" s="20"/>
@@ -1873,80 +1794,74 @@
       <c r="I35" s="20"/>
       <c r="J35" s="20"/>
       <c r="K35" s="20"/>
-      <c r="L35" s="1"/>
+      <c r="L35" s="2"/>
     </row>
     <row r="36" spans="1:12" customHeight="1" ht="23">
-      <c r="A36" s="1"/>
-      <c r="B36" s="8" t="s">
+      <c r="A36" s="15"/>
+      <c r="B36" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="7"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="51"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" customHeight="1" ht="23">
+      <c r="A37" s="15"/>
+      <c r="B37" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="7"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" spans="1:12" customHeight="1" ht="23">
+      <c r="A38" s="15"/>
+      <c r="B38" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="33"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="1"/>
-    </row>
-    <row r="37" spans="1:12" customHeight="1" ht="23">
-      <c r="A37" s="1"/>
-      <c r="B37" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="1"/>
-    </row>
-    <row r="38" spans="1:12" customHeight="1" ht="23">
-      <c r="A38" s="1"/>
-      <c r="B38" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="33"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="33"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="1"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="2"/>
     </row>
     <row r="39" spans="1:12" customHeight="1" ht="23">
-      <c r="A39" s="1"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="1"/>
+      <c r="A39" s="15"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12" customHeight="1" ht="23">
-      <c r="A40" s="1"/>
+      <c r="A40" s="15"/>
       <c r="B40" s="19" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="19"/>
@@ -1957,10 +1872,10 @@
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
-      <c r="L40" s="1"/>
+      <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" customHeight="1" ht="5">
-      <c r="A41" s="1"/>
+      <c r="A41" s="15"/>
       <c r="B41" s="20"/>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
@@ -1971,80 +1886,74 @@
       <c r="I41" s="20"/>
       <c r="J41" s="20"/>
       <c r="K41" s="20"/>
-      <c r="L41" s="1"/>
+      <c r="L41" s="2"/>
     </row>
     <row r="42" spans="1:12" customHeight="1" ht="23">
-      <c r="A42" s="1"/>
-      <c r="B42" s="8" t="s">
+      <c r="A42" s="15"/>
+      <c r="B42" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="7"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="51"/>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="1:12" customHeight="1" ht="23">
+      <c r="A43" s="15"/>
+      <c r="B43" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="7"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" spans="1:12" customHeight="1" ht="23">
+      <c r="A44" s="15"/>
+      <c r="B44" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="15"/>
-      <c r="L42" s="1"/>
-    </row>
-    <row r="43" spans="1:12" customHeight="1" ht="23">
-      <c r="A43" s="1"/>
-      <c r="B43" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="1"/>
-    </row>
-    <row r="44" spans="1:12" customHeight="1" ht="23">
-      <c r="A44" s="1"/>
-      <c r="B44" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" s="33"/>
-      <c r="E44" s="33"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="1"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="31"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12" customHeight="1" ht="23">
-      <c r="A45" s="1"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="1"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="2"/>
     </row>
     <row r="46" spans="1:12" customHeight="1" ht="23">
-      <c r="A46" s="1"/>
+      <c r="A46" s="15"/>
       <c r="B46" s="19" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C46" s="19"/>
       <c r="D46" s="19"/>
@@ -2055,10 +1964,10 @@
       <c r="I46" s="19"/>
       <c r="J46" s="19"/>
       <c r="K46" s="19"/>
-      <c r="L46" s="1"/>
+      <c r="L46" s="2"/>
     </row>
     <row r="47" spans="1:12" customHeight="1" ht="5">
-      <c r="A47" s="1"/>
+      <c r="A47" s="15"/>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
       <c r="D47" s="20"/>
@@ -2069,104 +1978,86 @@
       <c r="I47" s="20"/>
       <c r="J47" s="20"/>
       <c r="K47" s="20"/>
-      <c r="L47" s="1"/>
+      <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" customHeight="1" ht="23">
-      <c r="A48" s="1"/>
-      <c r="B48" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C48" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D48" s="27"/>
-      <c r="E48" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F48" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G48" s="27"/>
-      <c r="H48" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="I48" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="J48" s="29"/>
-      <c r="K48" s="9"/>
-      <c r="L48" s="1"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F48" s="8"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="I48" s="9"/>
+      <c r="J48" s="50"/>
+      <c r="K48" s="32"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" customHeight="1" ht="23">
-      <c r="A49" s="1"/>
-      <c r="B49" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C49" s="31"/>
-      <c r="D49" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="F49" s="26">
-        <v>234</v>
-      </c>
-      <c r="G49" s="27"/>
-      <c r="H49" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I49" s="28">
-        <v>3445</v>
-      </c>
-      <c r="J49" s="29"/>
-      <c r="K49" s="9"/>
-      <c r="L49" s="1"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="54"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F49" s="8"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" s="9"/>
+      <c r="J49" s="50"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" customHeight="1" ht="23">
-      <c r="A50" s="1"/>
-      <c r="B50" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C50" s="31"/>
-      <c r="D50" s="16">
-        <v>34</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F50" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G50" s="27"/>
-      <c r="H50" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="I50" s="28">
-        <v>43355</v>
-      </c>
-      <c r="J50" s="29"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="1"/>
+      <c r="A50" s="15"/>
+      <c r="B50" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C50" s="54"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="F50" s="8"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="I50" s="9"/>
+      <c r="J50" s="50"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="2"/>
     </row>
     <row r="51" spans="1:12" customHeight="1" ht="23">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="15"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15"/>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+      <c r="K51" s="15"/>
+      <c r="L51" s="2"/>
     </row>
     <row r="52" spans="1:12" customHeight="1" ht="23">
-      <c r="A52" s="1"/>
+      <c r="A52" s="15"/>
       <c r="B52" s="19" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="C52" s="19"/>
       <c r="D52" s="19"/>
@@ -2177,10 +2068,10 @@
       <c r="I52" s="19"/>
       <c r="J52" s="19"/>
       <c r="K52" s="19"/>
-      <c r="L52" s="1"/>
+      <c r="L52" s="2"/>
     </row>
     <row r="53" spans="1:12" customHeight="1" ht="5">
-      <c r="A53" s="1"/>
+      <c r="A53" s="15"/>
       <c r="B53" s="20"/>
       <c r="C53" s="20"/>
       <c r="D53" s="20"/>
@@ -2191,172 +2082,211 @@
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
       <c r="K53" s="20"/>
-      <c r="L53" s="1"/>
+      <c r="L53" s="2"/>
     </row>
     <row r="54" spans="1:12" customHeight="1" ht="23">
-      <c r="A54" s="1"/>
-      <c r="B54" s="21"/>
-      <c r="C54" s="22"/>
-      <c r="D54" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="24"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="25"/>
-      <c r="L54" s="1"/>
+      <c r="A54" s="15"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="52"/>
+      <c r="L54" s="2"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
+      <c r="A55" s="15"/>
+      <c r="B55" s="15"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="2"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="1"/>
-      <c r="B56" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="C56" s="18"/>
-      <c r="D56" s="18"/>
-      <c r="E56" s="18"/>
-      <c r="F56" s="18"/>
-      <c r="G56" s="18"/>
-      <c r="H56" s="18"/>
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
-      <c r="K56" s="18"/>
-      <c r="L56" s="1"/>
+      <c r="A56" s="15"/>
+      <c r="B56" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="27"/>
+      <c r="I56" s="27"/>
+      <c r="J56" s="27"/>
+      <c r="K56" s="27"/>
+      <c r="L56" s="2"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="1"/>
-      <c r="B57" s="18"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="18"/>
-      <c r="E57" s="18"/>
-      <c r="F57" s="18"/>
-      <c r="G57" s="18"/>
-      <c r="H57" s="18"/>
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
-      <c r="K57" s="18"/>
-      <c r="L57" s="1"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="27"/>
+      <c r="J57" s="27"/>
+      <c r="K57" s="27"/>
+      <c r="L57" s="2"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="1"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="18"/>
-      <c r="E58" s="18"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="18"/>
-      <c r="H58" s="18"/>
-      <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
-      <c r="K58" s="18"/>
-      <c r="L58" s="1"/>
+      <c r="A58" s="15"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
+      <c r="F58" s="27"/>
+      <c r="G58" s="27"/>
+      <c r="H58" s="27"/>
+      <c r="I58" s="27"/>
+      <c r="J58" s="27"/>
+      <c r="K58" s="27"/>
+      <c r="L58" s="2"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="1"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="18"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="18"/>
-      <c r="H59" s="18"/>
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="1"/>
+      <c r="A59" s="15"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+      <c r="K59" s="27"/>
+      <c r="L59" s="2"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="1"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="18"/>
-      <c r="H60" s="18"/>
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="1"/>
+      <c r="A60" s="15"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="27"/>
+      <c r="I60" s="27"/>
+      <c r="J60" s="27"/>
+      <c r="K60" s="27"/>
+      <c r="L60" s="2"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
     </row>
   </sheetData>
-  <sheetProtection password="9328" sheet="1" formatCells="0" formatColumns="0" formatRows="0"/>
+  <sheetProtection password="9328" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="1" insertRows="1" deleteColumns="1" deleteRows="1" sort="1" selectLockedCells="0" selectUnlockedCells="0"/>
   <mergeCells>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="B6:K6"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:K10"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="B11:K11"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="B3:K4"/>
+    <mergeCell ref="B56:K60"/>
+    <mergeCell ref="B52:K52"/>
+    <mergeCell ref="B53:K53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="E54:K54"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="B46:K46"/>
+    <mergeCell ref="B47:K47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="I48:J48"/>
+    <mergeCell ref="C38:J38"/>
+    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="B41:K41"/>
+    <mergeCell ref="C42:J42"/>
+    <mergeCell ref="C43:J43"/>
+    <mergeCell ref="C44:J44"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="B34:K34"/>
+    <mergeCell ref="B35:K35"/>
+    <mergeCell ref="C36:J36"/>
+    <mergeCell ref="C37:J37"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="B27:K27"/>
+    <mergeCell ref="B28:K28"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C14:J14"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:E23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
     <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
     <mergeCell ref="I23:K23"/>
     <mergeCell ref="B21:K21"/>
     <mergeCell ref="B22:K22"/>
@@ -2366,57 +2296,16 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B16:K16"/>
     <mergeCell ref="B17:K17"/>
-    <mergeCell ref="B27:K27"/>
-    <mergeCell ref="B28:K28"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="C44:J44"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="B34:K34"/>
-    <mergeCell ref="B35:K35"/>
-    <mergeCell ref="C36:J36"/>
-    <mergeCell ref="C37:J37"/>
-    <mergeCell ref="C38:J38"/>
-    <mergeCell ref="B40:K40"/>
-    <mergeCell ref="B41:K41"/>
-    <mergeCell ref="C42:J42"/>
-    <mergeCell ref="C43:J43"/>
-    <mergeCell ref="B46:K46"/>
-    <mergeCell ref="B47:K47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="I49:J49"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="I50:J50"/>
-    <mergeCell ref="B56:K60"/>
-    <mergeCell ref="B52:K52"/>
-    <mergeCell ref="B53:K53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="E54:K54"/>
+    <mergeCell ref="B10:K10"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B11:K11"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="B3:K4"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="B6:K6"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="G8:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:E8">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2428,55 +2317,67 @@
       <formula>LEN(TRIM($C$12))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D18:K18">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>LEN(TRIM($D$18))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D23:E23">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>LEN(TRIM($D$23))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I23:K23">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>LEN(TRIM($I$23))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D24:E24">
-    <cfRule type="expression" dxfId="3" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>LEN(TRIM($D$24))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D25:E25">
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="6" priority="7">
       <formula>LEN(TRIM($D$25))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D30:E30">
-    <cfRule type="expression" dxfId="5" priority="8">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>LEN(TRIM($D$30))=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D32:E32">
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>LEN(TRIM($D$32))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:K18">
-    <cfRule type="expression" dxfId="7" priority="3">
-      <formula>LEN(TRIM($D$18))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I23:K23">
-    <cfRule type="expression" dxfId="8" priority="5">
-      <formula>LEN(TRIM($I$23))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="7">
-    <dataValidation type="list" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D19">
+  <dataValidations count="11">
+    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D19">
       <formula1>"Nueva,Usada"</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D29">
+    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D29">
       <formula1>"USD,PESOS"</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D54">
+    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D54">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
-    <dataValidation type="list" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="I23">
+    <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="I23">
       <formula1>"Terrestre,Marítimo,Aéreo,Multimodal"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D30:D32 I30:I31">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D30">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="I30">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D31">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="I31">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D32">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="date" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Escribe una fecha real, por ejemplo 24/09/2026. Si tu Excel no la acepta así, escríbela con el formato de fecha de tu computadora." promptTitle="Fecha" prompt="Escribe la fecha, por ejemplo 24/09/2026." sqref="J8:K8">
@@ -2490,7 +2391,7 @@
   </dataValidations>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2501,133 +2402,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
   <dimension ref="A1:AN2"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="8.83203125" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="38" max="38" width="9.1640625" customWidth="true" style="0"/>
-    <col min="39" max="39" width="9.1640625" customWidth="true" style="0"/>
-    <col min="40" max="40" width="9.1640625" customWidth="true" style="0"/>
+    <col min="38" max="38" width="9.1" customWidth="true" style="0"/>
+    <col min="39" max="39" width="9.1" customWidth="true" style="0"/>
+    <col min="40" max="40" width="9.1" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="2" customFormat="1">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:40" s="3" customFormat="1">
+      <c r="A1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="AA1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="AB1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="AC1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="AD1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="AE1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="AF1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="AG1" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="AH1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="AI1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="AK1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="AL1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="AM1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="AN1" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="U1" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="V1" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="W1" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="X1" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Y1" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AG1" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AH1" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:40">
@@ -2643,73 +2544,73 @@
         <f>"Constancia"</f>
         <v>Constancia</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2">
         <f>Solicitud!C8</f>
-        <v>Jose Perea</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f>Solicitud!G8</f>
-        <v>5530050231</v>
-      </c>
-      <c r="F2" t="str">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <f>Solicitud!J8</f>
-        <v>24 petiembre 2026</v>
-      </c>
-      <c r="G2" t="str">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <f>Solicitud!C12</f>
-        <v>Patrick Perea</v>
-      </c>
-      <c r="H2" t="str">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <f>Solicitud!C13</f>
-        <v>Rancho del arco</v>
-      </c>
-      <c r="I2" t="str">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <f>Solicitud!C14</f>
-        <v>abuela</v>
-      </c>
-      <c r="J2" t="str">
+        <v>0</v>
+      </c>
+      <c r="J2">
         <f>Solicitud!D19</f>
-        <v>Nueva</v>
-      </c>
-      <c r="K2" t="str">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <f>Solicitud!D18</f>
-        <v>pantallas con IA</v>
-      </c>
-      <c r="L2" t="str">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <f>Solicitud!F19</f>
-        <v>27 "</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <f>Solicitud!D23</f>
-        <v>46289</v>
-      </c>
-      <c r="N2" t="str">
+        <v>0</v>
+      </c>
+      <c r="N2">
         <f>Solicitud!D24</f>
-        <v>pekin</v>
-      </c>
-      <c r="O2" t="str">
+        <v>0</v>
+      </c>
+      <c r="O2">
         <f>Solicitud!I24</f>
-        <v>china</v>
-      </c>
-      <c r="P2" t="str">
+        <v>0</v>
+      </c>
+      <c r="P2">
         <f>Solicitud!D25</f>
-        <v>cdmx</v>
-      </c>
-      <c r="Q2" t="str">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <f>Solicitud!I25</f>
-        <v>mexico</v>
-      </c>
-      <c r="R2" t="str">
+        <v>0</v>
+      </c>
+      <c r="R2">
         <f>Solicitud!I23</f>
-        <v>Marítimo</v>
-      </c>
-      <c r="S2" t="str">
+        <v>0</v>
+      </c>
+      <c r="S2">
         <f>IF(OR(UPPER(Solicitud!D29)="MXN",UPPER(Solicitud!D29)="PESOS"),"pesos",IF(UPPER(Solicitud!D29)="USD","usd",Solicitud!D29))</f>
-        <v>usd</v>
+        <v>0</v>
       </c>
       <c r="T2">
         <f>Solicitud!D30</f>
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="U2">
         <f>Solicitud!I30</f>
@@ -2725,77 +2626,77 @@
       </c>
       <c r="X2">
         <f>Solicitud!D32</f>
-        <v>3000</v>
-      </c>
-      <c r="Y2" t="str">
+        <v>0</v>
+      </c>
+      <c r="Y2">
         <f>Solicitud!C36</f>
-        <v>pepe consignatario</v>
-      </c>
-      <c r="Z2" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z2">
         <f>Solicitud!C37</f>
-        <v>xochimilco</v>
-      </c>
-      <c r="AA2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AA2">
         <f>Solicitud!C38</f>
-        <v>Roberto lona</v>
-      </c>
-      <c r="AB2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AB2">
         <f>Solicitud!C42</f>
-        <v>xang pei</v>
-      </c>
-      <c r="AC2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AC2">
         <f>Solicitud!C43</f>
-        <v>cerro de los remedios</v>
-      </c>
-      <c r="AD2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AD2">
         <f>Solicitud!C44</f>
-        <v>tsao</v>
-      </c>
-      <c r="AE2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE2">
         <f>Solicitud!C48</f>
-        <v>si</v>
-      </c>
-      <c r="AF2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AF2">
         <f>Solicitud!D49</f>
-        <v>ew34</v>
+        <v>0</v>
       </c>
       <c r="AG2">
         <f>Solicitud!D50</f>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AH2">
         <f>Solicitud!F49</f>
-        <v>234</v>
-      </c>
-      <c r="AI2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AI2">
         <f>Solicitud!F50</f>
-        <v>we34</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
         <f>Solicitud!I49</f>
-        <v>3445</v>
+        <v>0</v>
       </c>
       <c r="AK2">
         <f>Solicitud!I50</f>
-        <v>43355</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="str">
         <f>IF(UPPER(Solicitud!D54)="SI","si",IF(UPPER(Solicitud!D54)="SÍ","si",""))</f>
-        <v>si</v>
-      </c>
-      <c r="AM2" t="str">
+        <v/>
+      </c>
+      <c r="AM2">
         <f>Solicitud!F48</f>
-        <v>si</v>
-      </c>
-      <c r="AN2" t="str">
+        <v>0</v>
+      </c>
+      <c r="AN2">
         <f>Solicitud!I48</f>
-        <v>si</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection password="9328" sheet="1"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
 </worksheet>
 </file>
--- a/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
+++ b/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
@@ -20,16 +20,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
   <si>
-    <t>SOLICITUD DE ASEGURAMIENTO DE MERCANCIA</t>
-  </si>
-  <si>
-    <t>Completa únicamente las celdas en Azul claro. Envie este archivo Excel como adjunto, una solicitud por correo.</t>
+    <t>SOLICITUD DE ASEGURAMIENTO DE MERCANCÍA</t>
+  </si>
+  <si>
+    <t>Llena las celdas en azul claro; las marcadas en rojo son obligatorias. Envía una solicitud por archivo Excel.</t>
   </si>
   <si>
     <t>1. SOLICITANTE</t>
   </si>
   <si>
-    <t xml:space="preserve">Solicitante </t>
+    <t>Solicitante</t>
   </si>
   <si>
     <t>Teléfono</t>
@@ -38,7 +38,7 @@
     <t>Fecha</t>
   </si>
   <si>
-    <t>1. BENEFICIAROO DEL SEGURO</t>
+    <t>2. BENEFICIARIO DEL SEGURO</t>
   </si>
   <si>
     <t>Nombre</t>
@@ -50,7 +50,7 @@
     <t>Contacto</t>
   </si>
   <si>
-    <t>3. MERCANCIA POR ASEGURAR</t>
+    <t>3. MERCANCÍA POR ASEGURAR</t>
   </si>
   <si>
     <t>Mercancía asegurada</t>
@@ -83,7 +83,7 @@
     <t>País destino</t>
   </si>
   <si>
-    <t>5.CONCEPTOS POR ASEGURAR</t>
+    <t>5. CONCEPTOS POR ASEGURAR</t>
   </si>
   <si>
     <t>Moneda</t>
@@ -110,25 +110,25 @@
     <t>7. DATOS DEL PROVEEDOR</t>
   </si>
   <si>
-    <t>8.REFERENCIAS</t>
+    <t>8. REFERENCIAS</t>
   </si>
   <si>
     <t>Terrestre</t>
   </si>
   <si>
-    <t>Maritimo</t>
-  </si>
-  <si>
-    <t>Aereo</t>
-  </si>
-  <si>
-    <t>Talon embarque</t>
+    <t>Marítimo</t>
+  </si>
+  <si>
+    <t>Aéreo</t>
+  </si>
+  <si>
+    <t>Talón embarque</t>
   </si>
   <si>
     <t>B/L</t>
   </si>
   <si>
-    <t>N° Guia</t>
+    <t>N° Guía</t>
   </si>
   <si>
     <t>N° Contenedor o caja</t>
@@ -137,13 +137,13 @@
     <t>Contenedor</t>
   </si>
   <si>
-    <t>Linea aerea</t>
-  </si>
-  <si>
-    <t>9.DECLARACIÓN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acepto que la información declarada es verídica </t>
+    <t>Línea aérea</t>
+  </si>
+  <si>
+    <t>9. DECLARACIÓN</t>
+  </si>
+  <si>
+    <t>Acepto que la información declarada es verídica</t>
   </si>
   <si>
     <r>
@@ -2365,19 +2365,19 @@
     <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="I23">
       <formula1>"Terrestre,Marítimo,Aéreo,Multimodal"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D30">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="D30">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="I30">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="I30">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D31">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="D31">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="I31">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="I31">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Capture un monto numérico." sqref="D32">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="D32">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="date" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Escribe una fecha real, por ejemplo 24/09/2026. Si tu Excel no la acepta así, escríbela con el formato de fecha de tu computadora." promptTitle="Fecha" prompt="Escribe la fecha, por ejemplo 24/09/2026." sqref="J8:K8">

--- a/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
+++ b/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
@@ -171,7 +171,7 @@
       <t xml:space="preserve">
 Calle 29 Núm. 69 Col. Valentín Gómez Farías C.P. 15010, Venustiano Carranza, Ciudad de México, México
 Tel. Of. +52 (55) 8943-1208, +52 (55) 8943-6064
-www.jgmylard.com.mx</t>
+www.jgmylard.com</t>
     </r>
   </si>
   <si>
@@ -785,7 +785,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFBD5D5"/>
+          <bgColor rgb="FFFBD5D5"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2352,6 +2361,11 @@
       <formula>LEN(TRIM($D$32))=0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D29">
+    <cfRule type="expression" dxfId="9" priority="8">
+      <formula>LEN(TRIM($D$29))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="11">
     <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D19">
       <formula1>"Nueva,Usada"</formula1>

--- a/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
+++ b/docs/solicitud_aseguramiento_formato_jr_preparado.xlsx
@@ -303,7 +303,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -374,8 +374,28 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="10"/>
+      <color rgb="FFB42352"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="0"/>
+      <i val="1"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="10"/>
+      <color rgb="FFB42352"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -415,6 +435,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDFEBF7"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF0F4"/>
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
@@ -573,7 +599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="2" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
@@ -779,6 +805,26 @@
     </xf>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="165" fillId="8" borderId="2" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="8" borderId="8" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="2" borderId="3" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="7" numFmtId="0" fillId="2" borderId="9" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+      <protection locked="true"/>
+    </xf>
+    <xf xfId="0" fontId="8" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
       <protection locked="true"/>
     </xf>
   </cellXfs>
@@ -1751,14 +1797,20 @@
         <v>27</v>
       </c>
       <c r="C32" s="28"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="35"/>
+      <c r="D32" s="55" t="str">
+        <f>IF(COUNT(D30,I30,D31,I31)=0,"",SUM(D30,I30,D31,I31))</f>
+        <v/>
+      </c>
+      <c r="E32" s="56"/>
       <c r="F32" s="41"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="46"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
-      <c r="K32" s="47"/>
+      <c r="G32" s="57" t="str">
+        <f>IF(AND(ISNUMBER(D32),AND(D29="USD",OR(D32&lt;25,D32&gt;600000))),"Fuera de rango: USD 25 a 600,000",IF(AND(ISNUMBER(D32),AND(D29="PESOS",OR(D32&lt;500,D32&gt;12000000))),"Fuera de rango: MXN 500 a 12,000,000",""))</f>
+        <v/>
+      </c>
+      <c r="H32" s="58"/>
+      <c r="I32" s="59"/>
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" customHeight="1" ht="23">
@@ -2261,8 +2313,6 @@
     <mergeCell ref="C42:J42"/>
     <mergeCell ref="C43:J43"/>
     <mergeCell ref="C44:J44"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="I32:K32"/>
     <mergeCell ref="B34:K34"/>
     <mergeCell ref="B35:K35"/>
     <mergeCell ref="C36:J36"/>
@@ -2315,6 +2365,7 @@
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G32:K32"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:E8">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -2356,17 +2407,17 @@
       <formula>LEN(TRIM($D$30))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D32:E32">
-    <cfRule type="expression" dxfId="8" priority="9">
-      <formula>LEN(TRIM($D$32))=0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="D29">
-    <cfRule type="expression" dxfId="9" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>LEN(TRIM($D$29))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="11">
+  <conditionalFormatting sqref="D32:E32">
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>AND(ISNUMBER($D$32),OR(AND($D$29="USD",OR($D$32&lt;25,$D$32&gt;600000)),AND($D$29="PESOS",OR($D$32&lt;500,$D$32&gt;12000000))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="10">
     <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="D19">
       <formula1>"Nueva,Usada"</formula1>
     </dataValidation>
@@ -2379,19 +2430,16 @@
     <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Opción inválida" error="Selecciona una opción de la lista." sqref="I23">
       <formula1>"Terrestre,Marítimo,Aéreo,Multimodal"</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="D30">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Monto no válido" error="Captura una cantidad igual o mayor a 0, por ejemplo 150000.00." sqref="D30">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="I30">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Monto no válido" error="Captura una cantidad igual o mayor a 0, por ejemplo 150000.00." sqref="I30">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="D31">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Monto no válido" error="Captura una cantidad igual o mayor a 0, por ejemplo 150000.00." sqref="D31">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="I31">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Valor inválido" error="Captura un monto numérico." sqref="D32">
+    <dataValidation type="decimal" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="0" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Monto no válido" error="Captura una cantidad igual o mayor a 0, por ejemplo 150000.00." sqref="I31">
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="date" errorStyle="stop" operator="between" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" errorTitle="Fecha no válida" error="Escribe una fecha real, por ejemplo 24/09/2026. Si tu Excel no la acepta así, escríbela con el formato de fecha de tu computadora." promptTitle="Fecha" prompt="Escribe la fecha, por ejemplo 24/09/2026." sqref="J8:K8">
@@ -2638,9 +2686,9 @@
         <f>Solicitud!I31</f>
         <v>0</v>
       </c>
-      <c r="X2">
+      <c r="X2" t="str">
         <f>Solicitud!D32</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="Y2">
         <f>Solicitud!C36</f>
